--- a/ncxlxs/ncxlsx.xlsx
+++ b/ncxlxs/ncxlsx.xlsx
@@ -14205,10 +14205,10 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>전근대사 1</v>
+        <v>갑오개혁</v>
       </c>
       <c r="B2" t="str">
-        <v>근·현대 한국사 인물·사건·구호 등 발췌 1번 (내용을 수정해 사용하세요)</v>
+        <v>1894년 김홍집 내각이 단행한 조선의 재정·군사·교육 등 근대 제도 정비.</v>
       </c>
       <c r="C2" t="str">
         <v>중</v>
@@ -14219,10 +14219,10 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>전근대사 2</v>
+        <v>을미사변</v>
       </c>
       <c r="B3" t="str">
-        <v>근·현대 한국사 인물·사건·구호 등 발췌 2번 (내용을 수정해 사용하세요)</v>
+        <v>명성황후가 시해된 사건으로, 일본·러시아 등 열강의 조선 내 세력 다툼이 격화되었다.</v>
       </c>
       <c r="C3" t="str">
         <v>중</v>
@@ -14233,10 +14233,10 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>전근대사 3</v>
+        <v>독립협회</v>
       </c>
       <c r="B4" t="str">
-        <v>근·현대 한국사 인물·사건·구호 등 발췌 3번 (내용을 수정해 사용하세요)</v>
+        <v>서재필·이상재 등이 1896년에 세운 근대 정치 결사로, 만민공동회로 참정을 요구했다.</v>
       </c>
       <c r="C4" t="str">
         <v>중</v>
@@ -14247,10 +14247,10 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>전근대사 4</v>
+        <v>대한제국</v>
       </c>
       <c r="B5" t="str">
-        <v>근·현대 한국사 인물·사건·구호 등 발췌 4번 (내용을 수정해 사용하세요)</v>
+        <v>1897년 고종이 칭제를 칭하며 선포한 국호로, 제국 신분제 등이 정비되었다.</v>
       </c>
       <c r="C5" t="str">
         <v>중</v>
@@ -14261,10 +14261,10 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>전근대사 5</v>
+        <v>을사늑약</v>
       </c>
       <c r="B6" t="str">
-        <v>근·현대 한국사 인물·사건·구호 등 발췌 5번 (내용을 수정해 사용하세요)</v>
+        <v>1905년 일본이 외교·통상 등을 독점한 불평등 조약으로, 외교권을 빼앗겼다.</v>
       </c>
       <c r="C6" t="str">
         <v>중</v>
@@ -14275,10 +14275,10 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>전근대사 6</v>
+        <v>한일병합</v>
       </c>
       <c r="B7" t="str">
-        <v>근·현대 한국사 인물·사건·구호 등 발췌 6번 (내용을 수정해 사용하세요)</v>
+        <v>1910년 대한제국이 일본에 병합되며 국권을 상실하고 조선총독부가 설치되었다.</v>
       </c>
       <c r="C7" t="str">
         <v>중</v>
@@ -14289,10 +14289,10 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>전근대사 7</v>
+        <v>3·1운동</v>
       </c>
       <c r="B8" t="str">
-        <v>근·현대 한국사 인물·사건·구호 등 발췌 7번 (내용을 수정해 사용하세요)</v>
+        <v>1919년 전국에서 만세를 외치며 일제 식민 통치에 항거한 비폭력 독립 운동이다.</v>
       </c>
       <c r="C8" t="str">
         <v>중</v>
@@ -14303,10 +14303,10 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>전근대사 8</v>
+        <v>대한민국 임시정부</v>
       </c>
       <c r="B9" t="str">
-        <v>근·현대 한국사 인물·사건·구호 등 발췌 8번 (내용을 수정해 사용하세요)</v>
+        <v>1919년 상하이에서 수립된 독립운동의 중추로, 이승만·김구 등이 이끌었다.</v>
       </c>
       <c r="C9" t="str">
         <v>중</v>
@@ -14317,10 +14317,10 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>전근대사 9</v>
+        <v>봉오동 전투</v>
       </c>
       <c r="B10" t="str">
-        <v>근·현대 한국사 인물·사건·구호 등 발췌 9번 (내용을 수정해 사용하세요)</v>
+        <v>1920년 김좌진 부대가 일본 정규군과 맞붙어 큰 승리를 거둔 독립군 전투다.</v>
       </c>
       <c r="C10" t="str">
         <v>중</v>
@@ -14331,10 +14331,10 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>전근대사 10</v>
+        <v>청산리 대첩</v>
       </c>
       <c r="B11" t="str">
-        <v>근·현대 한국사 인물·사건·구호 등 발췌 10번 (내용을 수정해 사용하세요)</v>
+        <v>1920년 홍범도 부대가 일본군에게 큰 타격을 준 독립군의 승전으로 기억된다.</v>
       </c>
       <c r="C11" t="str">
         <v>중</v>
@@ -14345,10 +14345,10 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>전근대사 11</v>
+        <v>조선어학회</v>
       </c>
       <c r="B12" t="str">
-        <v>근·현대 한국사 인물·사건·구호 등 발췌 11번 (내용을 수정해 사용하세요)</v>
+        <v>한글 맞춤법 정리와 민족어 연구를 위해 1931년 전후 결성된 학술 단체다.</v>
       </c>
       <c r="C12" t="str">
         <v>중</v>
@@ -14359,10 +14359,10 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>전근대사 12</v>
+        <v>한글 맞춤법 통일안</v>
       </c>
       <c r="B13" t="str">
-        <v>근·현대 한국사 인물·사건·구호 등 발췌 12번 (내용을 수정해 사용하세요)</v>
+        <v>1933년 조선어학회가 정리한 표준 맞춤법으로, 오늘날 한글 규범의 토대가 되었다.</v>
       </c>
       <c r="C13" t="str">
         <v>중</v>
@@ -14373,10 +14373,10 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>전근대사 13</v>
+        <v>광복</v>
       </c>
       <c r="B14" t="str">
-        <v>근·현대 한국사 인물·사건·구호 등 발췌 13번 (내용을 수정해 사용하세요)</v>
+        <v>1945년 8·15 일본의 패망으로 조선이 일제 식민 지배에서 벗어난 해방을 뜻한다.</v>
       </c>
       <c r="C14" t="str">
         <v>중</v>
@@ -14387,10 +14387,10 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>전근대사 14</v>
+        <v>미·소 공동위원회</v>
       </c>
       <c r="B15" t="str">
-        <v>근·현대 한국사 인물·사건·구호 등 발췌 14번 (내용을 수정해 사용하세요)</v>
+        <v>해방 직후 미·소가 한반도 통일 정부 수립을 논의했으나 이견으로 결렬되었다.</v>
       </c>
       <c r="C15" t="str">
         <v>중</v>
@@ -14401,10 +14401,10 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>전근대사 15</v>
+        <v>신탁통치</v>
       </c>
       <c r="B16" t="str">
-        <v>근·현대 한국사 인물·사건·구호 등 발췌 15번 (내용을 수정해 사용하세요)</v>
+        <v>전후 한때 한반도를 연합국이 잠시 통치하자는 안으로, 찬반 논쟁이 격화되었다.</v>
       </c>
       <c r="C16" t="str">
         <v>중</v>
@@ -14415,10 +14415,10 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>전근대사 16</v>
+        <v>5·10 총선거</v>
       </c>
       <c r="B17" t="str">
-        <v>근·현대 한국사 인물·사건·구호 등 발췌 16번 (내용을 수정해 사용하세요)</v>
+        <v>1948년 제헌 국회의원을 뽑은 선거로, 대한민국 정부 수립의 토대가 되었다.</v>
       </c>
       <c r="C17" t="str">
         <v>중</v>
@@ -14429,10 +14429,10 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>전근대사 17</v>
+        <v>대한민국 정부 수립</v>
       </c>
       <c r="B18" t="str">
-        <v>근·현대 한국사 인물·사건·구호 등 발췌 17번 (내용을 수정해 사용하세요)</v>
+        <v>1948년 8월 이승만 대통령 취임과 함께 수립된 남한의 공식 정부다.</v>
       </c>
       <c r="C18" t="str">
         <v>중</v>
@@ -14443,10 +14443,10 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>전근대사 18</v>
+        <v>제헌 헌법</v>
       </c>
       <c r="B19" t="str">
-        <v>근·현대 한국사 인물·사건·구호 등 발췌 18번 (내용을 수정해 사용하세요)</v>
+        <v>1948년 제정된 대한민국 최초 헌법으로, 국민 주권·기본권 등을 선언했다.</v>
       </c>
       <c r="C19" t="str">
         <v>중</v>
@@ -14457,10 +14457,10 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>전근대사 19</v>
+        <v>6·25 전쟁</v>
       </c>
       <c r="B20" t="str">
-        <v>근·현대 한국사 인물·사건·구호 등 발췌 19번 (내용을 수정해 사용하세요)</v>
+        <v>1950년 북한의 남침으로 시작된 전쟁으로, 유엔군 참전과 인천 상륙 등이 있었다.</v>
       </c>
       <c r="C20" t="str">
         <v>중</v>
@@ -14471,10 +14471,10 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>전근대사 20</v>
+        <v>인천 상륙 작전</v>
       </c>
       <c r="B21" t="str">
-        <v>근·현대 한국사 인물·사건·구호 등 발췌 20번 (내용을 수정해 사용하세요)</v>
+        <v>1950년 맥아더가 지휘한 작전으로 전세가 역전되는 계기가 되었다.</v>
       </c>
       <c r="C21" t="str">
         <v>중</v>
@@ -14485,10 +14485,10 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>전근대사 21</v>
+        <v>휴전 협정</v>
       </c>
       <c r="B22" t="str">
-        <v>근·현대 한국사 인물·사건·구호 등 발췌 21번 (내용을 수정해 사용하세요)</v>
+        <v>1953년 군사 분계선 부근에서 체결되어 전투는 멈췄으나 평화 조약은 아니다.</v>
       </c>
       <c r="C22" t="str">
         <v>중</v>
@@ -14499,10 +14499,10 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>전근대사 22</v>
+        <v>4·19 혁명</v>
       </c>
       <c r="B23" t="str">
-        <v>근·현대 한국사 인물·사건·구호 등 발췌 22번 (내용을 수정해 사용하세요)</v>
+        <v>1960년 학생·시민이 부정 선거에 항의하며 독재에 맞선 민주화 운동이다.</v>
       </c>
       <c r="C23" t="str">
         <v>중</v>
@@ -14513,10 +14513,10 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>전근대사 23</v>
+        <v>5·16 군사정변</v>
       </c>
       <c r="B24" t="str">
-        <v>근·현대 한국사 인물·사건·구호 등 발췌 23번 (내용을 수정해 사용하세요)</v>
+        <v>1961년 박정희 등이 일으킨 쿠데타로, 장기 집권 체제로 이어졌다.</v>
       </c>
       <c r="C24" t="str">
         <v>중</v>
@@ -14527,10 +14527,10 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>전근대사 24</v>
+        <v>경제 개발 5개년 계획</v>
       </c>
       <c r="B25" t="str">
-        <v>근·현대 한국사 인물·사건·구호 등 발췌 24번 (내용을 수정해 사용하세요)</v>
+        <v>1960~70년대 정부가 추진한 산업화·수출 지향 성장 전략이다.</v>
       </c>
       <c r="C25" t="str">
         <v>중</v>
@@ -14541,10 +14541,10 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>전근대사 25</v>
+        <v>새마을 운동</v>
       </c>
       <c r="B26" t="str">
-        <v>근·현대 한국사 인물·사건·구호 등 발췌 25번 (내용을 수정해 사용하세요)</v>
+        <v>1970년대 농촌 근대화를 목표로 한 자조 운동으로, 도로·주택 개선에 초점을 두었다.</v>
       </c>
       <c r="C26" t="str">
         <v>중</v>
@@ -14555,10 +14555,10 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>전근대사 26</v>
+        <v>한일 기본조약</v>
       </c>
       <c r="B27" t="str">
-        <v>근·현대 한국사 인물·사건·구호 등 발췌 26번 (내용을 수정해 사용하세요)</v>
+        <v>1965년 체결되어 국교 정상화와 경제 협력의 토대를 마련했다.</v>
       </c>
       <c r="C27" t="str">
         <v>중</v>
@@ -14569,10 +14569,10 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>전근대사 27</v>
+        <v>베트남 파병</v>
       </c>
       <c r="B28" t="str">
-        <v>근·현대 한국사 인물·사건·구호 등 발췌 27번 (내용을 수정해 사용하세요)</v>
+        <v>1964~73년 미국의 요청에 따라 군·의료 등 파병을 보낸 사건이다.</v>
       </c>
       <c r="C28" t="str">
         <v>중</v>
@@ -14583,10 +14583,10 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>전근대사 28</v>
+        <v>유신 헌법</v>
       </c>
       <c r="B29" t="str">
-        <v>근·현대 한국사 인물·사건·구호 등 발췌 28번 (내용을 수정해 사용하세요)</v>
+        <v>1972년 대통령 연임·국회 임명 등을 가능케 한 헌법으로 비판을 받았다.</v>
       </c>
       <c r="C29" t="str">
         <v>중</v>
@@ -14597,10 +14597,10 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>전근대사 29</v>
+        <v>10·26 사건</v>
       </c>
       <c r="B30" t="str">
-        <v>근·현대 한국사 인물·사건·구호 등 발췌 29번 (내용을 수정해 사용하세요)</v>
+        <v>1979년 중앙정보부장이 박정희 대통령을 사살한 사건으로, 유신 체제가 흔들렸다.</v>
       </c>
       <c r="C30" t="str">
         <v>중</v>
@@ -14611,10 +14611,10 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>전근대사 30</v>
+        <v>12·12 군사반란</v>
       </c>
       <c r="B31" t="str">
-        <v>근·현대 한국사 인물·사건·구호 등 발췌 30번 (내용을 수정해 사용하세요)</v>
+        <v>1979년 전두환 세력이 군 내 주도권을 잡은 사태로 이어졌다.</v>
       </c>
       <c r="C31" t="str">
         <v>중</v>
@@ -14625,10 +14625,10 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>전근대사 31</v>
+        <v>5·17 비상계엄</v>
       </c>
       <c r="B32" t="str">
-        <v>근·현대 한국사 인물·사건·구호 등 발췌 31번 (내용을 수정해 사용하세요)</v>
+        <v>1980년 확대 계엄으로 정치 활동이 금지되고 민주화 세력이 탄압받았다.</v>
       </c>
       <c r="C32" t="str">
         <v>중</v>
@@ -14639,10 +14639,10 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>전근대사 32</v>
+        <v>5·18 민주화운동</v>
       </c>
       <c r="B33" t="str">
-        <v>근·현대 한국사 인물·사건·구호 등 발췌 32번 (내용을 수정해 사용하세요)</v>
+        <v>1980년 광주에서 시민이 계엄군에 맞서 항쟁한 사건으로, 민주 헌법의 정신적 토대가 되었다.</v>
       </c>
       <c r="C33" t="str">
         <v>중</v>
@@ -14653,10 +14653,10 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>전근대사 33</v>
+        <v>5공 화학</v>
       </c>
       <c r="B34" t="str">
-        <v>근·현대 한국사 인물·사건·구호 등 발췌 33번 (내용을 수정해 사용하세요)</v>
+        <v>전두환 정권이 5차 공화국 체제로 이어지며 강압 통치를 이어간 시기다.</v>
       </c>
       <c r="C34" t="str">
         <v>중</v>
@@ -14667,10 +14667,10 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>전근대사 34</v>
+        <v>6월 민주항쟁</v>
       </c>
       <c r="B35" t="str">
-        <v>근·현대 한국사 인물·사건·구호 등 발췌 34번 (내용을 수정해 사용하세요)</v>
+        <v>1987년 전국에서 촉발된 대통령 직선제 요구 운동으로, 6·29 선언으로 이어졌다.</v>
       </c>
       <c r="C35" t="str">
         <v>중</v>
@@ -14681,10 +14681,10 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>전근대사 35</v>
+        <v>6·29 선언</v>
       </c>
       <c r="B36" t="str">
-        <v>근·현대 한국사 인물·사건·구호 등 발췌 35번 (내용을 수정해 사용하세요)</v>
+        <v>노태우 후보가 직선제 개헌 등을 수용하겠다고 발표한 선언이다.</v>
       </c>
       <c r="C36" t="str">
         <v>중</v>
@@ -14695,10 +14695,10 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>전근대사 36</v>
+        <v>6공 화학</v>
       </c>
       <c r="B37" t="str">
-        <v>근·현대 한국사 인물·사건·구호 등 발췌 36번 (내용을 수정해 사용하세요)</v>
+        <v>노태우 정부 등 6차 공화국 시기로, 지방자치제 부활 등이 추진되었다.</v>
       </c>
       <c r="C37" t="str">
         <v>중</v>
@@ -14709,10 +14709,10 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>전근대사 37</v>
+        <v>한일 국교 정상화</v>
       </c>
       <c r="B38" t="str">
-        <v>근·현대 한국사 인물·사건·구호 등 발췌 37번 (내용을 수정해 사용하세요)</v>
+        <v>1965년 조약 체결을 가리키며, 경제·문화 교류가 본격화되었다.</v>
       </c>
       <c r="C38" t="str">
         <v>중</v>
@@ -14723,10 +14723,10 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>전근대사 38</v>
+        <v>남북 공동성명</v>
       </c>
       <c r="B39" t="str">
-        <v>근·현대 한국사 인물·사건·구호 등 발췌 38번 (내용을 수정해 사용하세요)</v>
+        <v>2000년 남북 정상회담에서 채택된 화해·교류·협력 선언이다.</v>
       </c>
       <c r="C39" t="str">
         <v>중</v>
@@ -14737,10 +14737,10 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>전근대사 39</v>
+        <v>금강산 관광</v>
       </c>
       <c r="B40" t="str">
-        <v>근·현대 한국사 인물·사건·구호 등 발췌 39번 (내용을 수정해 사용하세요)</v>
+        <v>1990년대 후반부터 이어진 남측 관광객의 북한 금강산 방문 사업이다.</v>
       </c>
       <c r="C40" t="str">
         <v>중</v>
@@ -14751,10 +14751,10 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>전근대사 40</v>
+        <v>개성 공단</v>
       </c>
       <c r="B41" t="str">
-        <v>근·현대 한국사 인물·사건·구호 등 발췌 40번 (내용을 수정해 사용하세요)</v>
+        <v>남북이 협력해 조성한 공업 단지로, 일자리·교류의 상징이었으나 중단되기도 했다.</v>
       </c>
       <c r="C41" t="str">
         <v>중</v>
@@ -14765,10 +14765,10 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>전근대사 41</v>
+        <v>6·25 전쟁 참전용사</v>
       </c>
       <c r="B42" t="str">
-        <v>근·현대 한국사 인물·사건·구호 등 발췌 41번 (내용을 수정해 사용하세요)</v>
+        <v>유엔군과 함께 자유를 지키려 싸운 한국군·연합군 장병을 기리는 말이다.</v>
       </c>
       <c r="C42" t="str">
         <v>중</v>
@@ -14779,10 +14779,10 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>전근대사 42</v>
+        <v>휴전선</v>
       </c>
       <c r="B43" t="str">
-        <v>근·현대 한국사 인물·사건·구호 등 발췌 42번 (내용을 수정해 사용하세요)</v>
+        <v>군사분계선을 따라 설치된 비무장 지대와 경계를 통틀어 이른다.</v>
       </c>
       <c r="C43" t="str">
         <v>중</v>
@@ -14793,10 +14793,10 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>전근대사 43</v>
+        <v>DMZ</v>
       </c>
       <c r="B44" t="str">
-        <v>근·현대 한국사 인물·사건·구호 등 발췌 43번 (내용을 수정해 사용하세요)</v>
+        <v>비무장지대로, 남북 사이 완충 구역이며 생태·역사적 가치가 있다.</v>
       </c>
       <c r="C44" t="str">
         <v>중</v>
@@ -14807,10 +14807,10 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>전근대사 44</v>
+        <v>판문점</v>
       </c>
       <c r="B45" t="str">
-        <v>근·현대 한국사 인물·사건·구호 등 발췌 44번 (내용을 수정해 사용하세요)</v>
+        <v>휴전 협정이 체결된 장소로, 남북 정상회담 등 외교 무대가 되었다.</v>
       </c>
       <c r="C45" t="str">
         <v>중</v>
@@ -14821,10 +14821,10 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>전근대사 45</v>
+        <v>남북 정상회담</v>
       </c>
       <c r="B46" t="str">
-        <v>근·현대 한국사 인물·사건·구호 등 발췌 45번 (내용을 수정해 사용하세요)</v>
+        <v>2000·2007·2018년 등 남북 수장이 만나 화해를 논의한 회담이다.</v>
       </c>
       <c r="C46" t="str">
         <v>중</v>
@@ -14835,10 +14835,10 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>전근대사 46</v>
+        <v>동학농민운동</v>
       </c>
       <c r="B47" t="str">
-        <v>근·현대 한국사 인물·사건·구호 등 발췌 46번 (내용을 수정해 사용하세요)</v>
+        <v>1894년 민란으로, 외세 침략과 탐관오리에 항거한 농민 봉기다.</v>
       </c>
       <c r="C47" t="str">
         <v>중</v>
@@ -14849,10 +14849,10 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>전근대사 47</v>
+        <v>을미의병</v>
       </c>
       <c r="B48" t="str">
-        <v>근·현대 한국사 인물·사건·구호 등 발췌 47번 (내용을 수정해 사용하세요)</v>
+        <v>을미사변에 항의하며 일어난 의병 항쟁이다.</v>
       </c>
       <c r="C48" t="str">
         <v>중</v>
@@ -14863,10 +14863,10 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>전근대사 48</v>
+        <v>을사의병</v>
       </c>
       <c r="B49" t="str">
-        <v>근·현대 한국사 인물·사건·구호 등 발췌 48번 (내용을 수정해 사용하세요)</v>
+        <v>을사늑약에 반발한 의병 운동이다.</v>
       </c>
       <c r="C49" t="str">
         <v>중</v>
@@ -14877,10 +14877,10 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>전근대사 49</v>
+        <v>국채보상운동</v>
       </c>
       <c r="B50" t="str">
-        <v>근·현대 한국사 인물·사건·구호 등 발췌 49번 (내용을 수정해 사용하세요)</v>
+        <v>일제의 국채 강매에 맞선 상인·시민의 저항 운동이다.</v>
       </c>
       <c r="C50" t="str">
         <v>중</v>
@@ -14891,10 +14891,10 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>전근대사 50</v>
+        <v>만세운동</v>
       </c>
       <c r="B51" t="str">
-        <v>근·현대 한국사 인물·사건·구호 등 발췌 50번 (내용을 수정해 사용하세요)</v>
+        <v>3·1운동 등에서 독립을 외친 상징적 구호와 시위 방식이다.</v>
       </c>
       <c r="C51" t="str">
         <v>중</v>
@@ -14905,10 +14905,10 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>전근대사 51</v>
+        <v>조선 총독부</v>
       </c>
       <c r="B52" t="str">
-        <v>근·현대 한국사 인물·사건·구호 등 발췌 51번 (내용을 수정해 사용하세요)</v>
+        <v>1910~1945년 일제가 한반도 통치 기구로 두었던 관청이다.</v>
       </c>
       <c r="C52" t="str">
         <v>중</v>
@@ -14919,10 +14919,10 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>전근대사 52</v>
+        <v>문화통치</v>
       </c>
       <c r="B53" t="str">
-        <v>근·현대 한국사 인물·사건·구호 등 발췌 52번 (내용을 수정해 사용하세요)</v>
+        <v>1920년대 일제가 민족 문화를 일부 허용하며 회유하려 한 정책이다.</v>
       </c>
       <c r="C53" t="str">
         <v>중</v>
@@ -14933,10 +14933,10 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>전근대사 53</v>
+        <v>민족말살통치</v>
       </c>
       <c r="B54" t="str">
-        <v>근·현대 한국사 인물·사건·구호 등 발췌 53번 (내용을 수정해 사용하세요)</v>
+        <v>1930년대 후반 창씨개명·황국신민화 등 민족 정체성을 지우려 한 탄압이다.</v>
       </c>
       <c r="C54" t="str">
         <v>중</v>
@@ -14947,10 +14947,10 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>전근대사 54</v>
+        <v>창씨개명</v>
       </c>
       <c r="B55" t="str">
-        <v>근·현대 한국사 인물·사건·구호 등 발췌 54번 (내용을 수정해 사용하세요)</v>
+        <v>일제가 한국인에게 일본식 성씨를 쓰게 강요한 정책이다.</v>
       </c>
       <c r="C55" t="str">
         <v>중</v>
@@ -14961,10 +14961,10 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>전근대사 55</v>
+        <v>징용</v>
       </c>
       <c r="B56" t="str">
-        <v>근·현대 한국사 인물·사건·구호 등 발췌 55번 (내용을 수정해 사용하세요)</v>
+        <v>일제가 전시에 한국인을 노동·군무에 강제 동원한 제도다.</v>
       </c>
       <c r="C56" t="str">
         <v>중</v>
@@ -14975,10 +14975,10 @@
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>전근대사 56</v>
+        <v>위안부</v>
       </c>
       <c r="B57" t="str">
-        <v>근·현대 한국사 인물·사건·구호 등 발췌 56번 (내용을 수정해 사용하세요)</v>
+        <v>일본군이 전시 성노예로 동원한 피해자 문제로, 인권·배상 논의가 이어진다.</v>
       </c>
       <c r="C57" t="str">
         <v>중</v>
@@ -14989,10 +14989,10 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>전근대사 57</v>
+        <v>광복회</v>
       </c>
       <c r="B58" t="str">
-        <v>근·현대 한국사 인물·사건·구호 등 발췌 57번 (내용을 수정해 사용하세요)</v>
+        <v>미국 등 해외에서 안창호 등이 조직한 비밀 결사로, 독립운동을 이어갔다.</v>
       </c>
       <c r="C58" t="str">
         <v>중</v>
@@ -15003,10 +15003,10 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>전근대사 58</v>
+        <v>흥사단</v>
       </c>
       <c r="B59" t="str">
-        <v>근·현대 한국사 인물·사건·구호 등 발췌 58번 (내용을 수정해 사용하세요)</v>
+        <v>일제 강점기 교육·계몽 활동을 한 단체로, 민족 교육에 힘썼다.</v>
       </c>
       <c r="C59" t="str">
         <v>중</v>
@@ -15017,10 +15017,10 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>전근대사 59</v>
+        <v>신간회</v>
       </c>
       <c r="B60" t="str">
-        <v>근·현대 한국사 인물·사건·구호 등 발췌 59번 (내용을 수정해 사용하세요)</v>
+        <v>1927년 좌우 합작으로 결성된 민족 운동 단체다.</v>
       </c>
       <c r="C60" t="str">
         <v>중</v>
@@ -15031,10 +15031,10 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>전근대사 60</v>
+        <v>근우회</v>
       </c>
       <c r="B61" t="str">
-        <v>근·현대 한국사 인물·사건·구호 등 발췌 60번 (내용을 수정해 사용하세요)</v>
+        <v>1920년대 여성 단체로, 계몽·권익 신장에 기여했다.</v>
       </c>
       <c r="C61" t="str">
         <v>중</v>
@@ -15045,10 +15045,10 @@
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>전근대사 61</v>
+        <v>KBS</v>
       </c>
       <c r="B62" t="str">
-        <v>근·현대 한국사 인물·사건·구호 등 발췌 61번 (내용을 수정해 사용하세요)</v>
+        <v>공영 방송으로, 민주 사회에서 공정 보도·문화 확산 역할을 한다.</v>
       </c>
       <c r="C62" t="str">
         <v>중</v>
@@ -15059,10 +15059,10 @@
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>전근대사 62</v>
+        <v>5·18 기념일</v>
       </c>
       <c r="B63" t="str">
-        <v>근·현대 한국사 인물·사건·구호 등 발췌 62번 (내용을 수정해 사용하세요)</v>
+        <v>광주 민주화운동을 기리는 국가 기념일로 제정되었다.</v>
       </c>
       <c r="C63" t="str">
         <v>중</v>
@@ -15073,10 +15073,10 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>전근대사 63</v>
+        <v>제헌절</v>
       </c>
       <c r="B64" t="str">
-        <v>근·현대 한국사 인물·사건·구호 등 발췌 63번 (내용을 수정해 사용하세요)</v>
+        <v>7월 17일, 1948년 제헌 헌법이 공포된 날을 기념한다.</v>
       </c>
       <c r="C64" t="str">
         <v>중</v>
@@ -15087,10 +15087,10 @@
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>전근대사 64</v>
+        <v>광복절</v>
       </c>
       <c r="B65" t="str">
-        <v>근·현대 한국사 인물·사건·구호 등 발췌 64번 (내용을 수정해 사용하세요)</v>
+        <v>8월 15일, 1945년 광복을 기념하는 국경일이다.</v>
       </c>
       <c r="C65" t="str">
         <v>중</v>
@@ -15101,10 +15101,10 @@
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>전근대사 65</v>
+        <v>개헌</v>
       </c>
       <c r="B66" t="str">
-        <v>근·현대 한국사 인물·사건·구호 등 발췌 65번 (내용을 수정해 사용하세요)</v>
+        <v>헌법 전부 또는 일부를 고치는 절차로, 국민투표 등이 동원되기도 한다.</v>
       </c>
       <c r="C66" t="str">
         <v>중</v>
@@ -15115,10 +15115,10 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>전근대사 66</v>
+        <v>직선제 개헌</v>
       </c>
       <c r="B67" t="str">
-        <v>근·현대 한국사 인물·사건·구호 등 발췌 66번 (내용을 수정해 사용하세요)</v>
+        <v>1987년 대통령을 국민이 직접 뽑도록 한 헌법 개정이다.</v>
       </c>
       <c r="C67" t="str">
         <v>중</v>
@@ -15129,10 +15129,10 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>전근대사 67</v>
+        <v>지방자치제</v>
       </c>
       <c r="B68" t="str">
-        <v>근·현대 한국사 인물·사건·구호 등 발췌 67번 (내용을 수정해 사용하세요)</v>
+        <v>1991년 지방의회 선거를 시작으로 주민 참여 행정이 본격화되었다.</v>
       </c>
       <c r="C68" t="str">
         <v>중</v>
@@ -15143,10 +15143,10 @@
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>전근대사 68</v>
+        <v>IMF 외환위기</v>
       </c>
       <c r="B69" t="str">
-        <v>근·현대 한국사 인물·사건·구호 등 발췌 68번 (내용을 수정해 사용하세요)</v>
+        <v>1997년 외환 부족으로 구제금융을 요청하며 경제 구조조정이 있었다.</v>
       </c>
       <c r="C69" t="str">
         <v>중</v>
@@ -15157,10 +15157,10 @@
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>전근대사 69</v>
+        <v>금 모으기 운동</v>
       </c>
       <c r="B70" t="str">
-        <v>근·현대 한국사 인물·사건·구호 등 발췌 69번 (내용을 수정해 사용하세요)</v>
+        <v>IMF 위기 때 국민이 금을 내놓아 외채 상환에 보탠 캠페인이다.</v>
       </c>
       <c r="C70" t="str">
         <v>중</v>
@@ -15171,10 +15171,10 @@
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>전근대사 70</v>
+        <v>디지털 뉴딜</v>
       </c>
       <c r="B71" t="str">
-        <v>근·현대 한국사 인물·사건·구호 등 발췌 70번 (내용을 수정해 사용하세요)</v>
+        <v>코로나 이후 디지털 인프라·일자리 투자를 늘리는 정책을 가리킨다.</v>
       </c>
       <c r="C71" t="str">
         <v>중</v>
@@ -15185,10 +15185,10 @@
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>전근대사 71</v>
+        <v>한반도 평화프로세스</v>
       </c>
       <c r="B72" t="str">
-        <v>근·현대 한국사 인물·사건·구호 등 발췌 71번 (내용을 수정해 사용하세요)</v>
+        <v>비핵화·평화 체제 등을 논의하는 남북·국제 외교 과정이다.</v>
       </c>
       <c r="C72" t="str">
         <v>중</v>
@@ -15199,10 +15199,10 @@
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>전근대사 72</v>
+        <v>남북 이산가족</v>
       </c>
       <c r="B73" t="str">
-        <v>근·현대 한국사 인물·사건·구호 등 발췌 72번 (내용을 수정해 사용하세요)</v>
+        <v>분단으로 헤어진 가족의 상봉·통신 문제를 뜻한다.</v>
       </c>
       <c r="C73" t="str">
         <v>중</v>
@@ -15213,10 +15213,10 @@
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>전근대사 73</v>
+        <v>월남</v>
       </c>
       <c r="B74" t="str">
-        <v>근·현대 한국사 인물·사건·구호 등 발췌 73번 (내용을 수정해 사용하세요)</v>
+        <v>한국전쟁 전후 남으로 피난한 이들의 이주를 말한다.</v>
       </c>
       <c r="C74" t="str">
         <v>중</v>
@@ -15227,10 +15227,10 @@
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>전근대사 74</v>
+        <v>북으로</v>
       </c>
       <c r="B75" t="str">
-        <v>근·현대 한국사 인물·사건·구호 등 발췌 74번 (내용을 수정해 사용하세요)</v>
+        <v>6·25 이후 북으로 머물거나 이주한 이들의 행로를 가리키기도 한다.</v>
       </c>
       <c r="C75" t="str">
         <v>중</v>
@@ -15241,10 +15241,10 @@
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>전근대사 75</v>
+        <v>이승만</v>
       </c>
       <c r="B76" t="str">
-        <v>근·현대 한국사 인물·사건·구호 등 발췌 75번 (내용을 수정해 사용하세요)</v>
+        <v>대한민국 초대 대통령으로, 정부 수립과 반공 노선을 강조했다.</v>
       </c>
       <c r="C76" t="str">
         <v>중</v>
@@ -15255,10 +15255,10 @@
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>전근대사 76</v>
+        <v>김구</v>
       </c>
       <c r="B77" t="str">
-        <v>근·현대 한국사 인물·사건·구호 등 발췌 76번 (내용을 수정해 사용하세요)</v>
+        <v>임시정부 주석으로 독립운동을 이끌었고 암살당하기 직전까지 활동했다.</v>
       </c>
       <c r="C77" t="str">
         <v>중</v>
@@ -15269,10 +15269,10 @@
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>전근대사 77</v>
+        <v>안중근</v>
       </c>
       <c r="B78" t="str">
-        <v>근·현대 한국사 인물·사건·구호 등 발췌 77번 (내용을 수정해 사용하세요)</v>
+        <v>하얼빈에서 이토 히로부미를 저격한 독립운동가다.</v>
       </c>
       <c r="C78" t="str">
         <v>중</v>
@@ -15283,10 +15283,10 @@
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>전근대사 78</v>
+        <v>윤봉길</v>
       </c>
       <c r="B79" t="str">
-        <v>근·현대 한국사 인물·사건·구호 등 발췌 78번 (내용을 수정해 사용하세요)</v>
+        <v>상하이 홍커우 공원 폭탄 의거를 단행한 의열투쟁가다.</v>
       </c>
       <c r="C79" t="str">
         <v>중</v>
@@ -15297,10 +15297,10 @@
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>전근대사 79</v>
+        <v>유관순</v>
       </c>
       <c r="B80" t="str">
-        <v>근·현대 한국사 인물·사건·구호 등 발췌 79번 (내용을 수정해 사용하세요)</v>
+        <v>3·1운동을 주도한 여성 독립운동가로, 순국했다.</v>
       </c>
       <c r="C80" t="str">
         <v>중</v>
@@ -15311,10 +15311,10 @@
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>전근대사 80</v>
+        <v>안창호</v>
       </c>
       <c r="B81" t="str">
-        <v>근·현대 한국사 인물·사건·구호 등 발췌 80번 (내용을 수정해 사용하세요)</v>
+        <v>교육·실력 양성을 강조한 독립운동가이자 흥사단 관련 인물이다.</v>
       </c>
       <c r="C81" t="str">
         <v>중</v>
@@ -15325,10 +15325,10 @@
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>전근대사 81</v>
+        <v>이상재</v>
       </c>
       <c r="B82" t="str">
-        <v>근·현대 한국사 인물·사건·구호 등 발췌 81번 (내용을 수정해 사용하세요)</v>
+        <v>독립협회와 교육 사업에 힘쓴 독립운동가다.</v>
       </c>
       <c r="C82" t="str">
         <v>중</v>
@@ -15339,10 +15339,10 @@
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>전근대사 82</v>
+        <v>서재필</v>
       </c>
       <c r="B83" t="str">
-        <v>근·현대 한국사 인물·사건·구호 등 발췌 82번 (내용을 수정해 사용하세요)</v>
+        <v>독립협회와 《독립신문》을 이끈 개화파 지식인이다.</v>
       </c>
       <c r="C83" t="str">
         <v>중</v>
@@ -15353,10 +15353,10 @@
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>전근대사 83</v>
+        <v>신채호</v>
       </c>
       <c r="B84" t="str">
-        <v>근·현대 한국사 인물·사건·구호 등 발췌 83번 (내용을 수정해 사용하세요)</v>
+        <v>《역사를 잊은 민족에게 미래는 없다》로 알려진 사학자·독립운동가다.</v>
       </c>
       <c r="C84" t="str">
         <v>중</v>
@@ -15367,10 +15367,10 @@
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>전근대사 84</v>
+        <v>박열</v>
       </c>
       <c r="B85" t="str">
-        <v>근·현대 한국사 인물·사건·구호 등 발췌 84번 (내용을 수정해 사용하세요)</v>
+        <v>일본에서 활동한 독립운동가로, 간첩 조작 사건으로 고초를 겪었다.</v>
       </c>
       <c r="C85" t="str">
         <v>중</v>
@@ -15381,10 +15381,10 @@
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>전근대사 85</v>
+        <v>김원봉</v>
       </c>
       <c r="B86" t="str">
-        <v>근·현대 한국사 인물·사건·구호 등 발췌 85번 (내용을 수정해 사용하세요)</v>
+        <v>조선인민혁명군 등과 관련된 독립운동가로, 광복 후 정치 활동도 했다.</v>
       </c>
       <c r="C86" t="str">
         <v>중</v>
@@ -15395,10 +15395,10 @@
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>전근대사 86</v>
+        <v>조봉암</v>
       </c>
       <c r="B87" t="str">
-        <v>근·현대 한국사 인물·사건·구호 등 발췌 86번 (내용을 수정해 사용하세요)</v>
+        <v>좌익 정당인으로, 남북 협상 시대에 활동했으나 사형되었다.</v>
       </c>
       <c r="C87" t="str">
         <v>중</v>
@@ -15409,10 +15409,10 @@
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>전근대사 87</v>
+        <v>장준하</v>
       </c>
       <c r="B88" t="str">
-        <v>근·현대 한국사 인물·사건·구호 등 발췌 87번 (내용을 수정해 사용하세요)</v>
+        <v>민족주의 언론인으로, 분단과 민족 문제를 논했다.</v>
       </c>
       <c r="C88" t="str">
         <v>중</v>
@@ -15423,10 +15423,10 @@
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>전근대사 88</v>
+        <v>김대중</v>
       </c>
       <c r="B89" t="str">
-        <v>근·현대 한국사 인물·사건·구호 등 발췌 88번 (내용을 수정해 사용하세요)</v>
+        <v>제15대 대통령으로, 햇볕정책과 노벨 평화상 수상이 있다.</v>
       </c>
       <c r="C89" t="str">
         <v>중</v>
@@ -15437,10 +15437,10 @@
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>전근대사 89</v>
+        <v>노무현</v>
       </c>
       <c r="B90" t="str">
-        <v>근·현대 한국사 인물·사건·구호 등 발췌 89번 (내용을 수정해 사용하세요)</v>
+        <v>제16대 대통령으로, 참여정부와 지역 균형 발전을 강조했다.</v>
       </c>
       <c r="C90" t="str">
         <v>중</v>
@@ -15451,10 +15451,10 @@
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>전근대사 90</v>
+        <v>박정희</v>
       </c>
       <c r="B91" t="str">
-        <v>근·현대 한국사 인물·사건·구호 등 발췌 90번 (내용을 수정해 사용하세요)</v>
+        <v>5·16 이후 장기 집권하며 수출 주도 산업화를 추진한 대통령이다.</v>
       </c>
       <c r="C91" t="str">
         <v>중</v>
@@ -15465,10 +15465,10 @@
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>전근대사 91</v>
+        <v>전두환</v>
       </c>
       <c r="B92" t="str">
-        <v>근·현대 한국사 인물·사건·구호 등 발췌 91번 (내용을 수정해 사용하세요)</v>
+        <v>5공 시기 대통령으로, 5·18 관련 재판에서 유죄 판결이 났다.</v>
       </c>
       <c r="C92" t="str">
         <v>중</v>
@@ -15479,10 +15479,10 @@
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>전근대사 92</v>
+        <v>노태우</v>
       </c>
       <c r="B93" t="str">
-        <v>근·현대 한국사 인물·사건·구호 등 발췌 92번 (내용을 수정해 사용하세요)</v>
+        <v>6공 초 대통령으로, 6·29 선언으로 직선제 수용에 기여했다.</v>
       </c>
       <c r="C93" t="str">
         <v>중</v>
@@ -15493,10 +15493,10 @@
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>전근대사 93</v>
+        <v>김영삼</v>
       </c>
       <c r="B94" t="str">
-        <v>근·현대 한국사 인물·사건·구호 등 발췌 93번 (내용을 수정해 사용하세요)</v>
+        <v>제14대 대통령으로, 금융 실명제·문민정부를 표방했다.</v>
       </c>
       <c r="C94" t="str">
         <v>중</v>
@@ -15507,10 +15507,10 @@
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>전근대사 94</v>
+        <v>이명박</v>
       </c>
       <c r="B95" t="str">
-        <v>근·현대 한국사 인물·사건·구호 등 발췌 94번 (내용을 수정해 사용하세요)</v>
+        <v>제17대 대통령으로, 4대강 사업 등 대규모 토목에 논란이 있었다.</v>
       </c>
       <c r="C95" t="str">
         <v>중</v>
@@ -15521,10 +15521,10 @@
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>전근대사 95</v>
+        <v>박근혜</v>
       </c>
       <c r="B96" t="str">
-        <v>근·현대 한국사 인물·사건·구호 등 발췌 95번 (내용을 수정해 사용하세요)</v>
+        <v>제18대 대통령으로, 탄핵으로 파면된 첫 사례가 되었다.</v>
       </c>
       <c r="C96" t="str">
         <v>중</v>
@@ -15535,10 +15535,10 @@
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>전근대사 96</v>
+        <v>문재인</v>
       </c>
       <c r="B97" t="str">
-        <v>근·현대 한국사 인물·사건·구호 등 발췌 96번 (내용을 수정해 사용하세요)</v>
+        <v>제19대 대통령으로, 남북 정상회담 등 평화 외교를 추진했다.</v>
       </c>
       <c r="C97" t="str">
         <v>중</v>
@@ -15549,10 +15549,10 @@
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>전근대사 97</v>
+        <v>윤석열</v>
       </c>
       <c r="B98" t="str">
-        <v>근·현대 한국사 인물·사건·구호 등 발췌 97번 (내용을 수정해 사용하세요)</v>
+        <v>제20대 대통령으로, 검찰 출신 첫 대통령이다.</v>
       </c>
       <c r="C98" t="str">
         <v>중</v>
@@ -15563,10 +15563,10 @@
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>전근대사 98</v>
+        <v>헌법재판소</v>
       </c>
       <c r="B99" t="str">
-        <v>근·현대 한국사 인물·사건·구호 등 발췌 98번 (내용을 수정해 사용하세요)</v>
+        <v>법률·탄핵 등 헌법 재판을 맡는 독립 기관이다.</v>
       </c>
       <c r="C99" t="str">
         <v>중</v>
@@ -15577,10 +15577,10 @@
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>전근대사 99</v>
+        <v>국회</v>
       </c>
       <c r="B100" t="str">
-        <v>근·현대 한국사 인물·사건·구호 등 발췌 99번 (내용을 수정해 사용하세요)</v>
+        <v>입법부로, 국민이 선출한 의원이 법률을 의결한다.</v>
       </c>
       <c r="C100" t="str">
         <v>중</v>
@@ -15591,10 +15591,10 @@
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>전근대사 100</v>
+        <v>대법원</v>
       </c>
       <c r="B101" t="str">
-        <v>근·현대 한국사 인물·사건·구호 등 발췌 100번 (내용을 수정해 사용하세요)</v>
+        <v>사법부 최종 심급으로, 판례를 통해 법을 해석한다.</v>
       </c>
       <c r="C101" t="str">
         <v>중</v>

--- a/ncxlxs/ncxlsx.xlsx
+++ b/ncxlxs/ncxlsx.xlsx
@@ -7298,7 +7298,6 @@
     <font>
       <color theme="1"/>
       <name val="Calibri"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="12.0"/>
@@ -7320,14 +7319,11 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
@@ -9256,1402 +9252,1402 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="2" t="s">
         <v>2220</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="2" t="s">
         <v>2221</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="2" t="s">
         <v>2222</v>
       </c>
-      <c r="D2" s="4">
+      <c r="D2" s="3">
         <v>1.0</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="2" t="s">
         <v>2223</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="2" t="s">
         <v>2224</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="2" t="s">
         <v>2222</v>
       </c>
-      <c r="D3" s="4">
+      <c r="D3" s="3">
         <v>2.0</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="2" t="s">
         <v>2225</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="2" t="s">
         <v>2226</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="2" t="s">
         <v>2222</v>
       </c>
-      <c r="D4" s="4">
+      <c r="D4" s="3">
         <v>3.0</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="2" t="s">
         <v>2227</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="2" t="s">
         <v>2228</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="2" t="s">
         <v>2222</v>
       </c>
-      <c r="D5" s="4">
+      <c r="D5" s="3">
         <v>3.0</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="2" t="s">
         <v>2229</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="2" t="s">
         <v>2230</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="2" t="s">
         <v>2222</v>
       </c>
-      <c r="D6" s="4">
+      <c r="D6" s="3">
         <v>1.0</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="2" t="s">
         <v>2231</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="2" t="s">
         <v>2232</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="2" t="s">
         <v>2222</v>
       </c>
-      <c r="D7" s="4">
+      <c r="D7" s="3">
         <v>1.0</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="2" t="s">
         <v>2233</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="2" t="s">
         <v>2234</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="2" t="s">
         <v>2222</v>
       </c>
-      <c r="D8" s="4">
+      <c r="D8" s="3">
         <v>1.0</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="2" t="s">
         <v>2235</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="2" t="s">
         <v>2236</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" s="2" t="s">
         <v>2222</v>
       </c>
-      <c r="D9" s="4">
+      <c r="D9" s="3">
         <v>4.0</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="2" t="s">
         <v>2237</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="2" t="s">
         <v>2238</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C10" s="2" t="s">
         <v>2222</v>
       </c>
-      <c r="D10" s="4">
+      <c r="D10" s="3">
         <v>4.0</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="2" t="s">
         <v>2239</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="2" t="s">
         <v>2240</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="C11" s="2" t="s">
         <v>2222</v>
       </c>
-      <c r="D11" s="4">
+      <c r="D11" s="3">
         <v>3.0</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="s">
+      <c r="A12" s="2" t="s">
         <v>2241</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="2" t="s">
         <v>2242</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="C12" s="2" t="s">
         <v>2222</v>
       </c>
-      <c r="D12" s="4">
+      <c r="D12" s="3">
         <v>2.0</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="s">
+      <c r="A13" s="2" t="s">
         <v>2243</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="2" t="s">
         <v>2244</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="C13" s="2" t="s">
         <v>2222</v>
       </c>
-      <c r="D13" s="4">
+      <c r="D13" s="3">
         <v>3.0</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="s">
+      <c r="A14" s="2" t="s">
         <v>2245</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="2" t="s">
         <v>2246</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="C14" s="2" t="s">
         <v>2222</v>
       </c>
-      <c r="D14" s="4">
+      <c r="D14" s="3">
         <v>3.0</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="s">
+      <c r="A15" s="2" t="s">
         <v>2247</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B15" s="2" t="s">
         <v>2248</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="C15" s="2" t="s">
         <v>2222</v>
       </c>
-      <c r="D15" s="4">
+      <c r="D15" s="3">
         <v>1.0</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="s">
+      <c r="A16" s="2" t="s">
         <v>2249</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B16" s="2" t="s">
         <v>2250</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="C16" s="2" t="s">
         <v>2222</v>
       </c>
-      <c r="D16" s="4">
+      <c r="D16" s="3">
         <v>2.0</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="s">
+      <c r="A17" s="2" t="s">
         <v>2251</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B17" s="2" t="s">
         <v>2252</v>
       </c>
-      <c r="C17" s="3" t="s">
+      <c r="C17" s="2" t="s">
         <v>2222</v>
       </c>
-      <c r="D17" s="4">
+      <c r="D17" s="3">
         <v>4.0</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="s">
+      <c r="A18" s="2" t="s">
         <v>2253</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B18" s="2" t="s">
         <v>2254</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="C18" s="2" t="s">
         <v>2222</v>
       </c>
-      <c r="D18" s="4">
+      <c r="D18" s="3">
         <v>4.0</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="s">
+      <c r="A19" s="2" t="s">
         <v>2255</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="B19" s="2" t="s">
         <v>2256</v>
       </c>
-      <c r="C19" s="3" t="s">
+      <c r="C19" s="2" t="s">
         <v>2222</v>
       </c>
-      <c r="D19" s="4">
+      <c r="D19" s="3">
         <v>3.0</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="s">
+      <c r="A20" s="2" t="s">
         <v>2257</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="B20" s="2" t="s">
         <v>2258</v>
       </c>
-      <c r="C20" s="3" t="s">
+      <c r="C20" s="2" t="s">
         <v>2222</v>
       </c>
-      <c r="D20" s="4">
+      <c r="D20" s="3">
         <v>3.0</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="3" t="s">
+      <c r="A21" s="2" t="s">
         <v>2259</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="B21" s="2" t="s">
         <v>2260</v>
       </c>
-      <c r="C21" s="3" t="s">
+      <c r="C21" s="2" t="s">
         <v>2222</v>
       </c>
-      <c r="D21" s="4">
+      <c r="D21" s="3">
         <v>2.0</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="3" t="s">
+      <c r="A22" s="2" t="s">
         <v>2261</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="B22" s="2" t="s">
         <v>2262</v>
       </c>
-      <c r="C22" s="3" t="s">
+      <c r="C22" s="2" t="s">
         <v>2222</v>
       </c>
-      <c r="D22" s="4">
+      <c r="D22" s="3">
         <v>1.0</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="3" t="s">
+      <c r="A23" s="2" t="s">
         <v>2263</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="B23" s="2" t="s">
         <v>2264</v>
       </c>
-      <c r="C23" s="3" t="s">
+      <c r="C23" s="2" t="s">
         <v>2222</v>
       </c>
-      <c r="D23" s="4">
+      <c r="D23" s="3">
         <v>2.0</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="3" t="s">
+      <c r="A24" s="2" t="s">
         <v>2265</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="B24" s="2" t="s">
         <v>2266</v>
       </c>
-      <c r="C24" s="3" t="s">
+      <c r="C24" s="2" t="s">
         <v>2222</v>
       </c>
-      <c r="D24" s="4">
+      <c r="D24" s="3">
         <v>2.0</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="3" t="s">
+      <c r="A25" s="2" t="s">
         <v>2267</v>
       </c>
-      <c r="B25" s="3" t="s">
+      <c r="B25" s="2" t="s">
         <v>2268</v>
       </c>
-      <c r="C25" s="3" t="s">
+      <c r="C25" s="2" t="s">
         <v>2222</v>
       </c>
-      <c r="D25" s="4">
+      <c r="D25" s="3">
         <v>2.0</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="3" t="s">
+      <c r="A26" s="2" t="s">
         <v>2269</v>
       </c>
-      <c r="B26" s="3" t="s">
+      <c r="B26" s="2" t="s">
         <v>2270</v>
       </c>
-      <c r="C26" s="3" t="s">
+      <c r="C26" s="2" t="s">
         <v>2222</v>
       </c>
-      <c r="D26" s="4">
+      <c r="D26" s="3">
         <v>2.0</v>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="3" t="s">
+      <c r="A27" s="2" t="s">
         <v>2271</v>
       </c>
-      <c r="B27" s="3" t="s">
+      <c r="B27" s="2" t="s">
         <v>2272</v>
       </c>
-      <c r="C27" s="3" t="s">
+      <c r="C27" s="2" t="s">
         <v>2222</v>
       </c>
-      <c r="D27" s="4">
+      <c r="D27" s="3">
         <v>4.0</v>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1">
-      <c r="A28" s="3" t="s">
+      <c r="A28" s="2" t="s">
         <v>2273</v>
       </c>
-      <c r="B28" s="3" t="s">
+      <c r="B28" s="2" t="s">
         <v>2274</v>
       </c>
-      <c r="C28" s="3" t="s">
+      <c r="C28" s="2" t="s">
         <v>2222</v>
       </c>
-      <c r="D28" s="4">
+      <c r="D28" s="3">
         <v>4.0</v>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1">
-      <c r="A29" s="3" t="s">
+      <c r="A29" s="2" t="s">
         <v>2275</v>
       </c>
-      <c r="B29" s="3" t="s">
+      <c r="B29" s="2" t="s">
         <v>2276</v>
       </c>
-      <c r="C29" s="3" t="s">
+      <c r="C29" s="2" t="s">
         <v>2222</v>
       </c>
-      <c r="D29" s="4">
+      <c r="D29" s="3">
         <v>2.0</v>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1">
-      <c r="A30" s="3" t="s">
+      <c r="A30" s="2" t="s">
         <v>2277</v>
       </c>
-      <c r="B30" s="3" t="s">
+      <c r="B30" s="2" t="s">
         <v>2278</v>
       </c>
-      <c r="C30" s="3" t="s">
+      <c r="C30" s="2" t="s">
         <v>2222</v>
       </c>
-      <c r="D30" s="4">
+      <c r="D30" s="3">
         <v>4.0</v>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1">
-      <c r="A31" s="3" t="s">
+      <c r="A31" s="2" t="s">
         <v>2279</v>
       </c>
-      <c r="B31" s="3" t="s">
+      <c r="B31" s="2" t="s">
         <v>2280</v>
       </c>
-      <c r="C31" s="3" t="s">
+      <c r="C31" s="2" t="s">
         <v>2222</v>
       </c>
-      <c r="D31" s="4">
+      <c r="D31" s="3">
         <v>1.0</v>
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1">
-      <c r="A32" s="3" t="s">
+      <c r="A32" s="2" t="s">
         <v>2281</v>
       </c>
-      <c r="B32" s="3" t="s">
+      <c r="B32" s="2" t="s">
         <v>2282</v>
       </c>
-      <c r="C32" s="3" t="s">
+      <c r="C32" s="2" t="s">
         <v>2222</v>
       </c>
-      <c r="D32" s="4">
+      <c r="D32" s="3">
         <v>4.0</v>
       </c>
     </row>
     <row r="33" ht="15.75" customHeight="1">
-      <c r="A33" s="3" t="s">
+      <c r="A33" s="2" t="s">
         <v>2283</v>
       </c>
-      <c r="B33" s="3" t="s">
+      <c r="B33" s="2" t="s">
         <v>2284</v>
       </c>
-      <c r="C33" s="3" t="s">
+      <c r="C33" s="2" t="s">
         <v>2222</v>
       </c>
-      <c r="D33" s="4">
+      <c r="D33" s="3">
         <v>3.0</v>
       </c>
     </row>
     <row r="34" ht="15.75" customHeight="1">
-      <c r="A34" s="3" t="s">
+      <c r="A34" s="2" t="s">
         <v>2285</v>
       </c>
-      <c r="B34" s="3" t="s">
+      <c r="B34" s="2" t="s">
         <v>2286</v>
       </c>
-      <c r="C34" s="3" t="s">
+      <c r="C34" s="2" t="s">
         <v>2222</v>
       </c>
-      <c r="D34" s="4">
+      <c r="D34" s="3">
         <v>2.0</v>
       </c>
     </row>
     <row r="35" ht="15.75" customHeight="1">
-      <c r="A35" s="3" t="s">
+      <c r="A35" s="2" t="s">
         <v>2287</v>
       </c>
-      <c r="B35" s="3" t="s">
+      <c r="B35" s="2" t="s">
         <v>2288</v>
       </c>
-      <c r="C35" s="3" t="s">
+      <c r="C35" s="2" t="s">
         <v>2222</v>
       </c>
-      <c r="D35" s="4">
+      <c r="D35" s="3">
         <v>3.0</v>
       </c>
     </row>
     <row r="36" ht="15.75" customHeight="1">
-      <c r="A36" s="3" t="s">
+      <c r="A36" s="2" t="s">
         <v>2289</v>
       </c>
-      <c r="B36" s="3" t="s">
+      <c r="B36" s="2" t="s">
         <v>2290</v>
       </c>
-      <c r="C36" s="3" t="s">
+      <c r="C36" s="2" t="s">
         <v>2222</v>
       </c>
-      <c r="D36" s="4">
+      <c r="D36" s="3">
         <v>3.0</v>
       </c>
     </row>
     <row r="37" ht="15.75" customHeight="1">
-      <c r="A37" s="3" t="s">
+      <c r="A37" s="2" t="s">
         <v>2291</v>
       </c>
-      <c r="B37" s="3" t="s">
+      <c r="B37" s="2" t="s">
         <v>2292</v>
       </c>
-      <c r="C37" s="3" t="s">
+      <c r="C37" s="2" t="s">
         <v>2222</v>
       </c>
-      <c r="D37" s="4">
+      <c r="D37" s="3">
         <v>1.0</v>
       </c>
     </row>
     <row r="38" ht="15.75" customHeight="1">
-      <c r="A38" s="3" t="s">
+      <c r="A38" s="2" t="s">
         <v>2293</v>
       </c>
-      <c r="B38" s="3" t="s">
+      <c r="B38" s="2" t="s">
         <v>2294</v>
       </c>
-      <c r="C38" s="3" t="s">
+      <c r="C38" s="2" t="s">
         <v>2222</v>
       </c>
-      <c r="D38" s="4">
+      <c r="D38" s="3">
         <v>3.0</v>
       </c>
     </row>
     <row r="39" ht="15.75" customHeight="1">
-      <c r="A39" s="3" t="s">
+      <c r="A39" s="2" t="s">
         <v>2295</v>
       </c>
-      <c r="B39" s="3" t="s">
+      <c r="B39" s="2" t="s">
         <v>2296</v>
       </c>
-      <c r="C39" s="3" t="s">
+      <c r="C39" s="2" t="s">
         <v>2222</v>
       </c>
-      <c r="D39" s="4">
+      <c r="D39" s="3">
         <v>2.0</v>
       </c>
     </row>
     <row r="40" ht="15.75" customHeight="1">
-      <c r="A40" s="3" t="s">
+      <c r="A40" s="2" t="s">
         <v>2297</v>
       </c>
-      <c r="B40" s="3" t="s">
+      <c r="B40" s="2" t="s">
         <v>2298</v>
       </c>
-      <c r="C40" s="3" t="s">
+      <c r="C40" s="2" t="s">
         <v>2222</v>
       </c>
-      <c r="D40" s="4">
+      <c r="D40" s="3">
         <v>3.0</v>
       </c>
     </row>
     <row r="41" ht="15.75" customHeight="1">
-      <c r="A41" s="3" t="s">
+      <c r="A41" s="2" t="s">
         <v>2299</v>
       </c>
-      <c r="B41" s="3" t="s">
+      <c r="B41" s="2" t="s">
         <v>2300</v>
       </c>
-      <c r="C41" s="3" t="s">
+      <c r="C41" s="2" t="s">
         <v>2222</v>
       </c>
-      <c r="D41" s="4">
+      <c r="D41" s="3">
         <v>4.0</v>
       </c>
     </row>
     <row r="42" ht="15.75" customHeight="1">
-      <c r="A42" s="3" t="s">
+      <c r="A42" s="2" t="s">
         <v>2301</v>
       </c>
-      <c r="B42" s="3" t="s">
+      <c r="B42" s="2" t="s">
         <v>2302</v>
       </c>
-      <c r="C42" s="3" t="s">
+      <c r="C42" s="2" t="s">
         <v>2222</v>
       </c>
-      <c r="D42" s="4">
+      <c r="D42" s="3">
         <v>2.0</v>
       </c>
     </row>
     <row r="43" ht="15.75" customHeight="1">
-      <c r="A43" s="3" t="s">
+      <c r="A43" s="2" t="s">
         <v>2303</v>
       </c>
-      <c r="B43" s="3" t="s">
+      <c r="B43" s="2" t="s">
         <v>2304</v>
       </c>
-      <c r="C43" s="3" t="s">
+      <c r="C43" s="2" t="s">
         <v>2222</v>
       </c>
-      <c r="D43" s="4">
+      <c r="D43" s="3">
         <v>1.0</v>
       </c>
     </row>
     <row r="44" ht="15.75" customHeight="1">
-      <c r="A44" s="3" t="s">
+      <c r="A44" s="2" t="s">
         <v>2305</v>
       </c>
-      <c r="B44" s="3" t="s">
+      <c r="B44" s="2" t="s">
         <v>2306</v>
       </c>
-      <c r="C44" s="3" t="s">
+      <c r="C44" s="2" t="s">
         <v>2222</v>
       </c>
-      <c r="D44" s="4">
+      <c r="D44" s="3">
         <v>4.0</v>
       </c>
     </row>
     <row r="45" ht="15.75" customHeight="1">
-      <c r="A45" s="3" t="s">
+      <c r="A45" s="2" t="s">
         <v>2307</v>
       </c>
-      <c r="B45" s="3" t="s">
+      <c r="B45" s="2" t="s">
         <v>2308</v>
       </c>
-      <c r="C45" s="3" t="s">
+      <c r="C45" s="2" t="s">
         <v>2222</v>
       </c>
-      <c r="D45" s="4">
+      <c r="D45" s="3">
         <v>3.0</v>
       </c>
     </row>
     <row r="46" ht="15.75" customHeight="1">
-      <c r="A46" s="3" t="s">
+      <c r="A46" s="2" t="s">
         <v>2309</v>
       </c>
-      <c r="B46" s="3" t="s">
+      <c r="B46" s="2" t="s">
         <v>2310</v>
       </c>
-      <c r="C46" s="3" t="s">
+      <c r="C46" s="2" t="s">
         <v>2222</v>
       </c>
-      <c r="D46" s="4">
+      <c r="D46" s="3">
         <v>4.0</v>
       </c>
     </row>
     <row r="47" ht="15.75" customHeight="1">
-      <c r="A47" s="3" t="s">
+      <c r="A47" s="2" t="s">
         <v>2311</v>
       </c>
-      <c r="B47" s="3" t="s">
+      <c r="B47" s="2" t="s">
         <v>2312</v>
       </c>
-      <c r="C47" s="3" t="s">
+      <c r="C47" s="2" t="s">
         <v>2222</v>
       </c>
-      <c r="D47" s="4">
+      <c r="D47" s="3">
         <v>3.0</v>
       </c>
     </row>
     <row r="48" ht="15.75" customHeight="1">
-      <c r="A48" s="3" t="s">
+      <c r="A48" s="2" t="s">
         <v>2313</v>
       </c>
-      <c r="B48" s="3" t="s">
+      <c r="B48" s="2" t="s">
         <v>2314</v>
       </c>
-      <c r="C48" s="3" t="s">
+      <c r="C48" s="2" t="s">
         <v>2222</v>
       </c>
-      <c r="D48" s="4">
+      <c r="D48" s="3">
         <v>4.0</v>
       </c>
     </row>
     <row r="49" ht="15.75" customHeight="1">
-      <c r="A49" s="3" t="s">
+      <c r="A49" s="2" t="s">
         <v>2315</v>
       </c>
-      <c r="B49" s="3" t="s">
+      <c r="B49" s="2" t="s">
         <v>2316</v>
       </c>
-      <c r="C49" s="3" t="s">
+      <c r="C49" s="2" t="s">
         <v>2222</v>
       </c>
-      <c r="D49" s="4">
+      <c r="D49" s="3">
         <v>4.0</v>
       </c>
     </row>
     <row r="50" ht="15.75" customHeight="1">
-      <c r="A50" s="3" t="s">
+      <c r="A50" s="2" t="s">
         <v>2317</v>
       </c>
-      <c r="B50" s="3" t="s">
+      <c r="B50" s="2" t="s">
         <v>2318</v>
       </c>
-      <c r="C50" s="3" t="s">
+      <c r="C50" s="2" t="s">
         <v>2222</v>
       </c>
-      <c r="D50" s="4">
+      <c r="D50" s="3">
         <v>2.0</v>
       </c>
     </row>
     <row r="51" ht="15.75" customHeight="1">
-      <c r="A51" s="3" t="s">
+      <c r="A51" s="2" t="s">
         <v>2319</v>
       </c>
-      <c r="B51" s="3" t="s">
+      <c r="B51" s="2" t="s">
         <v>2320</v>
       </c>
-      <c r="C51" s="3" t="s">
+      <c r="C51" s="2" t="s">
         <v>2222</v>
       </c>
-      <c r="D51" s="4">
+      <c r="D51" s="3">
         <v>3.0</v>
       </c>
     </row>
     <row r="52" ht="15.75" customHeight="1">
-      <c r="A52" s="3" t="s">
+      <c r="A52" s="2" t="s">
         <v>2321</v>
       </c>
-      <c r="B52" s="3" t="s">
+      <c r="B52" s="2" t="s">
         <v>2322</v>
       </c>
-      <c r="C52" s="3" t="s">
+      <c r="C52" s="2" t="s">
         <v>2222</v>
       </c>
-      <c r="D52" s="4">
+      <c r="D52" s="3">
         <v>4.0</v>
       </c>
     </row>
     <row r="53" ht="15.75" customHeight="1">
-      <c r="A53" s="3" t="s">
+      <c r="A53" s="2" t="s">
         <v>2323</v>
       </c>
-      <c r="B53" s="3" t="s">
+      <c r="B53" s="2" t="s">
         <v>2324</v>
       </c>
-      <c r="C53" s="3" t="s">
+      <c r="C53" s="2" t="s">
         <v>2222</v>
       </c>
-      <c r="D53" s="4">
+      <c r="D53" s="3">
         <v>2.0</v>
       </c>
     </row>
     <row r="54" ht="15.75" customHeight="1">
-      <c r="A54" s="3" t="s">
+      <c r="A54" s="2" t="s">
         <v>2325</v>
       </c>
-      <c r="B54" s="3" t="s">
+      <c r="B54" s="2" t="s">
         <v>2326</v>
       </c>
-      <c r="C54" s="3" t="s">
+      <c r="C54" s="2" t="s">
         <v>2222</v>
       </c>
-      <c r="D54" s="4">
+      <c r="D54" s="3">
         <v>3.0</v>
       </c>
     </row>
     <row r="55" ht="15.75" customHeight="1">
-      <c r="A55" s="3" t="s">
+      <c r="A55" s="2" t="s">
         <v>2327</v>
       </c>
-      <c r="B55" s="3" t="s">
+      <c r="B55" s="2" t="s">
         <v>2328</v>
       </c>
-      <c r="C55" s="3" t="s">
+      <c r="C55" s="2" t="s">
         <v>2222</v>
       </c>
-      <c r="D55" s="4">
+      <c r="D55" s="3">
         <v>3.0</v>
       </c>
     </row>
     <row r="56" ht="15.75" customHeight="1">
-      <c r="A56" s="3" t="s">
+      <c r="A56" s="2" t="s">
         <v>2329</v>
       </c>
-      <c r="B56" s="3" t="s">
+      <c r="B56" s="2" t="s">
         <v>2330</v>
       </c>
-      <c r="C56" s="3" t="s">
+      <c r="C56" s="2" t="s">
         <v>2222</v>
       </c>
-      <c r="D56" s="4">
+      <c r="D56" s="3">
         <v>3.0</v>
       </c>
     </row>
     <row r="57" ht="15.75" customHeight="1">
-      <c r="A57" s="3" t="s">
+      <c r="A57" s="2" t="s">
         <v>2331</v>
       </c>
-      <c r="B57" s="3" t="s">
+      <c r="B57" s="2" t="s">
         <v>2332</v>
       </c>
-      <c r="C57" s="3" t="s">
+      <c r="C57" s="2" t="s">
         <v>2222</v>
       </c>
-      <c r="D57" s="4">
+      <c r="D57" s="3">
         <v>2.0</v>
       </c>
     </row>
     <row r="58" ht="15.75" customHeight="1">
-      <c r="A58" s="3" t="s">
+      <c r="A58" s="2" t="s">
         <v>2333</v>
       </c>
-      <c r="B58" s="3" t="s">
+      <c r="B58" s="2" t="s">
         <v>2334</v>
       </c>
-      <c r="C58" s="3" t="s">
+      <c r="C58" s="2" t="s">
         <v>2222</v>
       </c>
-      <c r="D58" s="4">
+      <c r="D58" s="3">
         <v>2.0</v>
       </c>
     </row>
     <row r="59" ht="15.75" customHeight="1">
-      <c r="A59" s="3" t="s">
+      <c r="A59" s="2" t="s">
         <v>2335</v>
       </c>
-      <c r="B59" s="3" t="s">
+      <c r="B59" s="2" t="s">
         <v>2336</v>
       </c>
-      <c r="C59" s="3" t="s">
+      <c r="C59" s="2" t="s">
         <v>2222</v>
       </c>
-      <c r="D59" s="4">
+      <c r="D59" s="3">
         <v>1.0</v>
       </c>
     </row>
     <row r="60" ht="15.75" customHeight="1">
-      <c r="A60" s="3" t="s">
+      <c r="A60" s="2" t="s">
         <v>2337</v>
       </c>
-      <c r="B60" s="3" t="s">
+      <c r="B60" s="2" t="s">
         <v>2338</v>
       </c>
-      <c r="C60" s="3" t="s">
+      <c r="C60" s="2" t="s">
         <v>2222</v>
       </c>
-      <c r="D60" s="4">
+      <c r="D60" s="3">
         <v>2.0</v>
       </c>
     </row>
     <row r="61" ht="15.75" customHeight="1">
-      <c r="A61" s="3" t="s">
+      <c r="A61" s="2" t="s">
         <v>2339</v>
       </c>
-      <c r="B61" s="3" t="s">
+      <c r="B61" s="2" t="s">
         <v>2340</v>
       </c>
-      <c r="C61" s="3" t="s">
+      <c r="C61" s="2" t="s">
         <v>2222</v>
       </c>
-      <c r="D61" s="4">
+      <c r="D61" s="3">
         <v>4.0</v>
       </c>
     </row>
     <row r="62" ht="15.75" customHeight="1">
-      <c r="A62" s="3" t="s">
+      <c r="A62" s="2" t="s">
         <v>2341</v>
       </c>
-      <c r="B62" s="3" t="s">
+      <c r="B62" s="2" t="s">
         <v>2342</v>
       </c>
-      <c r="C62" s="3" t="s">
+      <c r="C62" s="2" t="s">
         <v>2222</v>
       </c>
-      <c r="D62" s="4">
+      <c r="D62" s="3">
         <v>4.0</v>
       </c>
     </row>
     <row r="63" ht="15.75" customHeight="1">
-      <c r="A63" s="3" t="s">
+      <c r="A63" s="2" t="s">
         <v>2343</v>
       </c>
-      <c r="B63" s="3" t="s">
+      <c r="B63" s="2" t="s">
         <v>2344</v>
       </c>
-      <c r="C63" s="3" t="s">
+      <c r="C63" s="2" t="s">
         <v>2222</v>
       </c>
-      <c r="D63" s="4">
+      <c r="D63" s="3">
         <v>3.0</v>
       </c>
     </row>
     <row r="64" ht="15.75" customHeight="1">
-      <c r="A64" s="3" t="s">
+      <c r="A64" s="2" t="s">
         <v>2345</v>
       </c>
-      <c r="B64" s="3" t="s">
+      <c r="B64" s="2" t="s">
         <v>2346</v>
       </c>
-      <c r="C64" s="3" t="s">
+      <c r="C64" s="2" t="s">
         <v>2222</v>
       </c>
-      <c r="D64" s="4">
+      <c r="D64" s="3">
         <v>1.0</v>
       </c>
     </row>
     <row r="65" ht="15.75" customHeight="1">
-      <c r="A65" s="3" t="s">
+      <c r="A65" s="2" t="s">
         <v>2347</v>
       </c>
-      <c r="B65" s="3" t="s">
+      <c r="B65" s="2" t="s">
         <v>2348</v>
       </c>
-      <c r="C65" s="3" t="s">
+      <c r="C65" s="2" t="s">
         <v>2222</v>
       </c>
-      <c r="D65" s="4">
+      <c r="D65" s="3">
         <v>2.0</v>
       </c>
     </row>
     <row r="66" ht="15.75" customHeight="1">
-      <c r="A66" s="3" t="s">
+      <c r="A66" s="2" t="s">
         <v>2349</v>
       </c>
-      <c r="B66" s="3" t="s">
+      <c r="B66" s="2" t="s">
         <v>2350</v>
       </c>
-      <c r="C66" s="3" t="s">
+      <c r="C66" s="2" t="s">
         <v>2222</v>
       </c>
-      <c r="D66" s="4">
+      <c r="D66" s="3">
         <v>1.0</v>
       </c>
     </row>
     <row r="67" ht="15.75" customHeight="1">
-      <c r="A67" s="3" t="s">
+      <c r="A67" s="2" t="s">
         <v>2351</v>
       </c>
-      <c r="B67" s="3" t="s">
+      <c r="B67" s="2" t="s">
         <v>2352</v>
       </c>
-      <c r="C67" s="3" t="s">
+      <c r="C67" s="2" t="s">
         <v>2222</v>
       </c>
-      <c r="D67" s="4">
+      <c r="D67" s="3">
         <v>3.0</v>
       </c>
     </row>
     <row r="68" ht="15.75" customHeight="1">
-      <c r="A68" s="3" t="s">
+      <c r="A68" s="2" t="s">
         <v>2353</v>
       </c>
-      <c r="B68" s="3" t="s">
+      <c r="B68" s="2" t="s">
         <v>2354</v>
       </c>
-      <c r="C68" s="3" t="s">
+      <c r="C68" s="2" t="s">
         <v>2222</v>
       </c>
-      <c r="D68" s="4">
+      <c r="D68" s="3">
         <v>4.0</v>
       </c>
     </row>
     <row r="69" ht="15.75" customHeight="1">
-      <c r="A69" s="3" t="s">
+      <c r="A69" s="2" t="s">
         <v>2355</v>
       </c>
-      <c r="B69" s="3" t="s">
+      <c r="B69" s="2" t="s">
         <v>2356</v>
       </c>
-      <c r="C69" s="3" t="s">
+      <c r="C69" s="2" t="s">
         <v>2222</v>
       </c>
-      <c r="D69" s="4">
+      <c r="D69" s="3">
         <v>3.0</v>
       </c>
     </row>
     <row r="70" ht="15.75" customHeight="1">
-      <c r="A70" s="3" t="s">
+      <c r="A70" s="2" t="s">
         <v>2357</v>
       </c>
-      <c r="B70" s="3" t="s">
+      <c r="B70" s="2" t="s">
         <v>2358</v>
       </c>
-      <c r="C70" s="3" t="s">
+      <c r="C70" s="2" t="s">
         <v>2222</v>
       </c>
-      <c r="D70" s="4">
+      <c r="D70" s="3">
         <v>4.0</v>
       </c>
     </row>
     <row r="71" ht="15.75" customHeight="1">
-      <c r="A71" s="3" t="s">
+      <c r="A71" s="2" t="s">
         <v>2359</v>
       </c>
-      <c r="B71" s="3" t="s">
+      <c r="B71" s="2" t="s">
         <v>2360</v>
       </c>
-      <c r="C71" s="3" t="s">
+      <c r="C71" s="2" t="s">
         <v>2222</v>
       </c>
-      <c r="D71" s="4">
+      <c r="D71" s="3">
         <v>4.0</v>
       </c>
     </row>
     <row r="72" ht="15.75" customHeight="1">
-      <c r="A72" s="3" t="s">
+      <c r="A72" s="2" t="s">
         <v>2361</v>
       </c>
-      <c r="B72" s="3" t="s">
+      <c r="B72" s="2" t="s">
         <v>2362</v>
       </c>
-      <c r="C72" s="3" t="s">
+      <c r="C72" s="2" t="s">
         <v>2222</v>
       </c>
-      <c r="D72" s="4">
+      <c r="D72" s="3">
         <v>4.0</v>
       </c>
     </row>
     <row r="73" ht="15.75" customHeight="1">
-      <c r="A73" s="3" t="s">
+      <c r="A73" s="2" t="s">
         <v>2363</v>
       </c>
-      <c r="B73" s="3" t="s">
+      <c r="B73" s="2" t="s">
         <v>2364</v>
       </c>
-      <c r="C73" s="3" t="s">
+      <c r="C73" s="2" t="s">
         <v>2222</v>
       </c>
-      <c r="D73" s="4">
+      <c r="D73" s="3">
         <v>4.0</v>
       </c>
     </row>
     <row r="74" ht="15.75" customHeight="1">
-      <c r="A74" s="3" t="s">
+      <c r="A74" s="2" t="s">
         <v>2365</v>
       </c>
-      <c r="B74" s="3" t="s">
+      <c r="B74" s="2" t="s">
         <v>2366</v>
       </c>
-      <c r="C74" s="3" t="s">
+      <c r="C74" s="2" t="s">
         <v>2222</v>
       </c>
-      <c r="D74" s="4">
+      <c r="D74" s="3">
         <v>3.0</v>
       </c>
     </row>
     <row r="75" ht="15.75" customHeight="1">
-      <c r="A75" s="3" t="s">
+      <c r="A75" s="2" t="s">
         <v>2367</v>
       </c>
-      <c r="B75" s="3" t="s">
+      <c r="B75" s="2" t="s">
         <v>2368</v>
       </c>
-      <c r="C75" s="3" t="s">
+      <c r="C75" s="2" t="s">
         <v>2222</v>
       </c>
-      <c r="D75" s="4">
+      <c r="D75" s="3">
         <v>1.0</v>
       </c>
     </row>
     <row r="76" ht="15.75" customHeight="1">
-      <c r="A76" s="3" t="s">
+      <c r="A76" s="2" t="s">
         <v>2369</v>
       </c>
-      <c r="B76" s="3" t="s">
+      <c r="B76" s="2" t="s">
         <v>2370</v>
       </c>
-      <c r="C76" s="3" t="s">
+      <c r="C76" s="2" t="s">
         <v>2222</v>
       </c>
-      <c r="D76" s="4">
+      <c r="D76" s="3">
         <v>1.0</v>
       </c>
     </row>
     <row r="77" ht="15.75" customHeight="1">
-      <c r="A77" s="3" t="s">
+      <c r="A77" s="2" t="s">
         <v>2371</v>
       </c>
-      <c r="B77" s="3" t="s">
+      <c r="B77" s="2" t="s">
         <v>2372</v>
       </c>
-      <c r="C77" s="3" t="s">
+      <c r="C77" s="2" t="s">
         <v>2222</v>
       </c>
-      <c r="D77" s="4">
+      <c r="D77" s="3">
         <v>2.0</v>
       </c>
     </row>
     <row r="78" ht="15.75" customHeight="1">
-      <c r="A78" s="3" t="s">
+      <c r="A78" s="2" t="s">
         <v>2373</v>
       </c>
-      <c r="B78" s="3" t="s">
+      <c r="B78" s="2" t="s">
         <v>2374</v>
       </c>
-      <c r="C78" s="3" t="s">
+      <c r="C78" s="2" t="s">
         <v>2222</v>
       </c>
-      <c r="D78" s="4">
+      <c r="D78" s="3">
         <v>3.0</v>
       </c>
     </row>
     <row r="79" ht="15.75" customHeight="1">
-      <c r="A79" s="3" t="s">
+      <c r="A79" s="2" t="s">
         <v>2375</v>
       </c>
-      <c r="B79" s="3" t="s">
+      <c r="B79" s="2" t="s">
         <v>2376</v>
       </c>
-      <c r="C79" s="3" t="s">
+      <c r="C79" s="2" t="s">
         <v>2222</v>
       </c>
-      <c r="D79" s="4">
+      <c r="D79" s="3">
         <v>1.0</v>
       </c>
     </row>
     <row r="80" ht="15.75" customHeight="1">
-      <c r="A80" s="3" t="s">
+      <c r="A80" s="2" t="s">
         <v>2377</v>
       </c>
-      <c r="B80" s="3" t="s">
+      <c r="B80" s="2" t="s">
         <v>2378</v>
       </c>
-      <c r="C80" s="3" t="s">
+      <c r="C80" s="2" t="s">
         <v>2222</v>
       </c>
-      <c r="D80" s="4">
+      <c r="D80" s="3">
         <v>2.0</v>
       </c>
     </row>
     <row r="81" ht="15.75" customHeight="1">
-      <c r="A81" s="3" t="s">
+      <c r="A81" s="2" t="s">
         <v>2379</v>
       </c>
-      <c r="B81" s="3" t="s">
+      <c r="B81" s="2" t="s">
         <v>2380</v>
       </c>
-      <c r="C81" s="3" t="s">
+      <c r="C81" s="2" t="s">
         <v>2222</v>
       </c>
-      <c r="D81" s="4">
+      <c r="D81" s="3">
         <v>3.0</v>
       </c>
     </row>
     <row r="82" ht="15.75" customHeight="1">
-      <c r="A82" s="3" t="s">
+      <c r="A82" s="2" t="s">
         <v>2381</v>
       </c>
-      <c r="B82" s="3" t="s">
+      <c r="B82" s="2" t="s">
         <v>2382</v>
       </c>
-      <c r="C82" s="3" t="s">
+      <c r="C82" s="2" t="s">
         <v>2222</v>
       </c>
-      <c r="D82" s="4">
+      <c r="D82" s="3">
         <v>3.0</v>
       </c>
     </row>
     <row r="83" ht="15.75" customHeight="1">
-      <c r="A83" s="3" t="s">
+      <c r="A83" s="2" t="s">
         <v>2383</v>
       </c>
-      <c r="B83" s="3" t="s">
+      <c r="B83" s="2" t="s">
         <v>2384</v>
       </c>
-      <c r="C83" s="3" t="s">
+      <c r="C83" s="2" t="s">
         <v>2222</v>
       </c>
-      <c r="D83" s="4">
+      <c r="D83" s="3">
         <v>3.0</v>
       </c>
     </row>
     <row r="84" ht="15.75" customHeight="1">
-      <c r="A84" s="3" t="s">
+      <c r="A84" s="2" t="s">
         <v>2385</v>
       </c>
-      <c r="B84" s="3" t="s">
+      <c r="B84" s="2" t="s">
         <v>2386</v>
       </c>
-      <c r="C84" s="3" t="s">
+      <c r="C84" s="2" t="s">
         <v>2222</v>
       </c>
-      <c r="D84" s="4">
+      <c r="D84" s="3">
         <v>2.0</v>
       </c>
     </row>
     <row r="85" ht="15.75" customHeight="1">
-      <c r="A85" s="3" t="s">
+      <c r="A85" s="2" t="s">
         <v>2387</v>
       </c>
-      <c r="B85" s="3" t="s">
+      <c r="B85" s="2" t="s">
         <v>2388</v>
       </c>
-      <c r="C85" s="3" t="s">
+      <c r="C85" s="2" t="s">
         <v>2222</v>
       </c>
-      <c r="D85" s="4">
+      <c r="D85" s="3">
         <v>3.0</v>
       </c>
     </row>
     <row r="86" ht="15.75" customHeight="1">
-      <c r="A86" s="3" t="s">
+      <c r="A86" s="2" t="s">
         <v>2389</v>
       </c>
-      <c r="B86" s="3" t="s">
+      <c r="B86" s="2" t="s">
         <v>2390</v>
       </c>
-      <c r="C86" s="3" t="s">
+      <c r="C86" s="2" t="s">
         <v>2222</v>
       </c>
-      <c r="D86" s="4">
+      <c r="D86" s="3">
         <v>4.0</v>
       </c>
     </row>
     <row r="87" ht="15.75" customHeight="1">
-      <c r="A87" s="3" t="s">
+      <c r="A87" s="2" t="s">
         <v>2391</v>
       </c>
-      <c r="B87" s="3" t="s">
+      <c r="B87" s="2" t="s">
         <v>2392</v>
       </c>
-      <c r="C87" s="3" t="s">
+      <c r="C87" s="2" t="s">
         <v>2222</v>
       </c>
-      <c r="D87" s="4">
+      <c r="D87" s="3">
         <v>4.0</v>
       </c>
     </row>
     <row r="88" ht="15.75" customHeight="1">
-      <c r="A88" s="3" t="s">
+      <c r="A88" s="2" t="s">
         <v>2393</v>
       </c>
-      <c r="B88" s="3" t="s">
+      <c r="B88" s="2" t="s">
         <v>2394</v>
       </c>
-      <c r="C88" s="3" t="s">
+      <c r="C88" s="2" t="s">
         <v>2222</v>
       </c>
-      <c r="D88" s="4">
+      <c r="D88" s="3">
         <v>4.0</v>
       </c>
     </row>
     <row r="89" ht="15.75" customHeight="1">
-      <c r="A89" s="3" t="s">
+      <c r="A89" s="2" t="s">
         <v>2395</v>
       </c>
-      <c r="B89" s="3" t="s">
+      <c r="B89" s="2" t="s">
         <v>2396</v>
       </c>
-      <c r="C89" s="3" t="s">
+      <c r="C89" s="2" t="s">
         <v>2222</v>
       </c>
-      <c r="D89" s="4">
+      <c r="D89" s="3">
         <v>3.0</v>
       </c>
     </row>
     <row r="90" ht="15.75" customHeight="1">
-      <c r="A90" s="3" t="s">
+      <c r="A90" s="2" t="s">
         <v>2397</v>
       </c>
-      <c r="B90" s="3" t="s">
+      <c r="B90" s="2" t="s">
         <v>2398</v>
       </c>
-      <c r="C90" s="3" t="s">
+      <c r="C90" s="2" t="s">
         <v>2222</v>
       </c>
-      <c r="D90" s="4">
+      <c r="D90" s="3">
         <v>4.0</v>
       </c>
     </row>
     <row r="91" ht="15.75" customHeight="1">
-      <c r="A91" s="3" t="s">
+      <c r="A91" s="2" t="s">
         <v>2399</v>
       </c>
-      <c r="B91" s="3" t="s">
+      <c r="B91" s="2" t="s">
         <v>2400</v>
       </c>
-      <c r="C91" s="3" t="s">
+      <c r="C91" s="2" t="s">
         <v>2222</v>
       </c>
-      <c r="D91" s="4">
+      <c r="D91" s="3">
         <v>3.0</v>
       </c>
     </row>
     <row r="92" ht="15.75" customHeight="1">
-      <c r="A92" s="3" t="s">
+      <c r="A92" s="2" t="s">
         <v>2401</v>
       </c>
-      <c r="B92" s="3" t="s">
+      <c r="B92" s="2" t="s">
         <v>2402</v>
       </c>
-      <c r="C92" s="3" t="s">
+      <c r="C92" s="2" t="s">
         <v>2222</v>
       </c>
-      <c r="D92" s="4">
+      <c r="D92" s="3">
         <v>2.0</v>
       </c>
     </row>
     <row r="93" ht="15.75" customHeight="1">
-      <c r="A93" s="3" t="s">
+      <c r="A93" s="2" t="s">
         <v>2403</v>
       </c>
-      <c r="B93" s="3" t="s">
+      <c r="B93" s="2" t="s">
         <v>2404</v>
       </c>
-      <c r="C93" s="3" t="s">
+      <c r="C93" s="2" t="s">
         <v>2222</v>
       </c>
-      <c r="D93" s="4">
+      <c r="D93" s="3">
         <v>4.0</v>
       </c>
     </row>
     <row r="94" ht="15.75" customHeight="1">
-      <c r="A94" s="3" t="s">
+      <c r="A94" s="2" t="s">
         <v>2405</v>
       </c>
-      <c r="B94" s="3" t="s">
+      <c r="B94" s="2" t="s">
         <v>2406</v>
       </c>
-      <c r="C94" s="3" t="s">
+      <c r="C94" s="2" t="s">
         <v>2222</v>
       </c>
-      <c r="D94" s="4">
+      <c r="D94" s="3">
         <v>4.0</v>
       </c>
     </row>
     <row r="95" ht="15.75" customHeight="1">
-      <c r="A95" s="3" t="s">
+      <c r="A95" s="2" t="s">
         <v>2407</v>
       </c>
-      <c r="B95" s="3" t="s">
+      <c r="B95" s="2" t="s">
         <v>2408</v>
       </c>
-      <c r="C95" s="3" t="s">
+      <c r="C95" s="2" t="s">
         <v>2222</v>
       </c>
-      <c r="D95" s="4">
+      <c r="D95" s="3">
         <v>3.0</v>
       </c>
     </row>
     <row r="96" ht="15.75" customHeight="1">
-      <c r="A96" s="3" t="s">
+      <c r="A96" s="2" t="s">
         <v>2409</v>
       </c>
-      <c r="B96" s="3" t="s">
+      <c r="B96" s="2" t="s">
         <v>2410</v>
       </c>
-      <c r="C96" s="3" t="s">
+      <c r="C96" s="2" t="s">
         <v>2222</v>
       </c>
-      <c r="D96" s="4">
+      <c r="D96" s="3">
         <v>3.0</v>
       </c>
     </row>
     <row r="97" ht="15.75" customHeight="1">
-      <c r="A97" s="3" t="s">
+      <c r="A97" s="2" t="s">
         <v>2411</v>
       </c>
-      <c r="B97" s="3" t="s">
+      <c r="B97" s="2" t="s">
         <v>2412</v>
       </c>
-      <c r="C97" s="3" t="s">
+      <c r="C97" s="2" t="s">
         <v>2222</v>
       </c>
-      <c r="D97" s="4">
+      <c r="D97" s="3">
         <v>4.0</v>
       </c>
     </row>
     <row r="98" ht="15.75" customHeight="1">
-      <c r="A98" s="3" t="s">
+      <c r="A98" s="2" t="s">
         <v>2413</v>
       </c>
-      <c r="B98" s="3" t="s">
+      <c r="B98" s="2" t="s">
         <v>2414</v>
       </c>
-      <c r="C98" s="3" t="s">
+      <c r="C98" s="2" t="s">
         <v>2222</v>
       </c>
-      <c r="D98" s="4">
+      <c r="D98" s="3">
         <v>3.0</v>
       </c>
     </row>
     <row r="99" ht="15.75" customHeight="1">
-      <c r="A99" s="3" t="s">
+      <c r="A99" s="2" t="s">
         <v>2415</v>
       </c>
-      <c r="B99" s="3" t="s">
+      <c r="B99" s="2" t="s">
         <v>2416</v>
       </c>
-      <c r="C99" s="3" t="s">
+      <c r="C99" s="2" t="s">
         <v>2222</v>
       </c>
-      <c r="D99" s="4">
+      <c r="D99" s="3">
         <v>3.0</v>
       </c>
     </row>
     <row r="100" ht="15.75" customHeight="1">
-      <c r="A100" s="3" t="s">
+      <c r="A100" s="2" t="s">
         <v>2417</v>
       </c>
-      <c r="B100" s="3" t="s">
+      <c r="B100" s="2" t="s">
         <v>2418</v>
       </c>
-      <c r="C100" s="3" t="s">
+      <c r="C100" s="2" t="s">
         <v>2222</v>
       </c>
-      <c r="D100" s="4">
+      <c r="D100" s="3">
         <v>2.0</v>
       </c>
     </row>
@@ -11584,702 +11580,702 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="D2" s="2">
+      <c r="D2" s="1">
         <v>3.0</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="D3" s="2">
+      <c r="D3" s="1">
         <v>2.0</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="D4" s="2">
+      <c r="D4" s="1">
         <v>1.0</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="D5" s="2">
+      <c r="D5" s="1">
         <v>3.0</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="D6" s="2">
+      <c r="D6" s="1">
         <v>1.0</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="D7" s="2">
+      <c r="D7" s="1">
         <v>2.0</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="s">
+      <c r="A8" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="D8" s="2">
+      <c r="D8" s="1">
         <v>4.0</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="s">
+      <c r="A9" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="D9" s="2">
+      <c r="D9" s="1">
         <v>2.0</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="s">
+      <c r="A10" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C10" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="D10" s="2">
+      <c r="D10" s="1">
         <v>3.0</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="s">
+      <c r="A11" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C11" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="D11" s="2">
+      <c r="D11" s="1">
         <v>3.0</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="s">
+      <c r="A12" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="C12" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="D12" s="2">
+      <c r="D12" s="1">
         <v>2.0</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="s">
+      <c r="A13" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B13" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="C13" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="D13" s="2">
+      <c r="D13" s="1">
         <v>2.0</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="s">
+      <c r="A14" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B14" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="C14" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="D14" s="2">
+      <c r="D14" s="1">
         <v>2.0</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="s">
+      <c r="A15" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="B15" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="C15" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="D15" s="2">
+      <c r="D15" s="1">
         <v>2.0</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="s">
+      <c r="A16" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="B16" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="C16" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="D16" s="2">
+      <c r="D16" s="1">
         <v>2.0</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="s">
+      <c r="A17" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="B17" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="C17" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="D17" s="2">
+      <c r="D17" s="1">
         <v>2.0</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="s">
+      <c r="A18" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="B18" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="C18" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="D18" s="2">
+      <c r="D18" s="1">
         <v>2.0</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="s">
+      <c r="A19" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="B19" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="C19" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="D19" s="2">
+      <c r="D19" s="1">
         <v>2.0</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="s">
+      <c r="A20" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="B20" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="C20" s="2" t="s">
+      <c r="C20" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="D20" s="2">
+      <c r="D20" s="1">
         <v>2.0</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="s">
+      <c r="A21" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B21" s="2" t="s">
+      <c r="B21" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="C21" s="2" t="s">
+      <c r="C21" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="D21" s="2">
+      <c r="D21" s="1">
         <v>2.0</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="s">
+      <c r="A22" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="B22" s="2" t="s">
+      <c r="B22" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="C22" s="2" t="s">
+      <c r="C22" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="D22" s="2">
+      <c r="D22" s="1">
         <v>2.0</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="s">
+      <c r="A23" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="B23" s="2" t="s">
+      <c r="B23" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="C23" s="2" t="s">
+      <c r="C23" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="D23" s="2">
+      <c r="D23" s="1">
         <v>2.0</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="s">
+      <c r="A24" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="B24" s="2" t="s">
+      <c r="B24" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="C24" s="2" t="s">
+      <c r="C24" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="D24" s="2">
+      <c r="D24" s="1">
         <v>2.0</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="s">
+      <c r="A25" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="B25" s="2" t="s">
+      <c r="B25" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="C25" s="2" t="s">
+      <c r="C25" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="D25" s="2">
+      <c r="D25" s="1">
         <v>2.0</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="s">
+      <c r="A26" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="B26" s="2" t="s">
+      <c r="B26" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="C26" s="2" t="s">
+      <c r="C26" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="D26" s="2">
+      <c r="D26" s="1">
         <v>2.0</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="s">
+      <c r="A27" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="B27" s="2" t="s">
+      <c r="B27" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="C27" s="2" t="s">
+      <c r="C27" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="D27" s="2">
+      <c r="D27" s="1">
         <v>2.0</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="s">
+      <c r="A28" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="B28" s="2" t="s">
+      <c r="B28" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="C28" s="2" t="s">
+      <c r="C28" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="D28" s="2">
+      <c r="D28" s="1">
         <v>2.0</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="s">
+      <c r="A29" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="B29" s="2" t="s">
+      <c r="B29" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="C29" s="2" t="s">
+      <c r="C29" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="D29" s="2">
+      <c r="D29" s="1">
         <v>2.0</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="s">
+      <c r="A30" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="B30" s="2" t="s">
+      <c r="B30" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="C30" s="2" t="s">
+      <c r="C30" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="D30" s="2">
+      <c r="D30" s="1">
         <v>2.0</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="s">
+      <c r="A31" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="B31" s="2" t="s">
+      <c r="B31" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="C31" s="2" t="s">
+      <c r="C31" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="D31" s="2">
+      <c r="D31" s="1">
         <v>2.0</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="s">
+      <c r="A32" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="B32" s="2" t="s">
+      <c r="B32" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="C32" s="2" t="s">
+      <c r="C32" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="D32" s="2">
+      <c r="D32" s="1">
         <v>2.0</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="s">
+      <c r="A33" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="B33" s="2" t="s">
+      <c r="B33" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="C33" s="2" t="s">
+      <c r="C33" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="D33" s="2">
+      <c r="D33" s="1">
         <v>2.0</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="s">
+      <c r="A34" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="B34" s="2" t="s">
+      <c r="B34" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="C34" s="2" t="s">
+      <c r="C34" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="D34" s="2">
+      <c r="D34" s="1">
         <v>2.0</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="s">
+      <c r="A35" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="B35" s="2" t="s">
+      <c r="B35" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="C35" s="2" t="s">
+      <c r="C35" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="D35" s="2">
+      <c r="D35" s="1">
         <v>2.0</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="s">
+      <c r="A36" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="B36" s="2" t="s">
+      <c r="B36" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="C36" s="2" t="s">
+      <c r="C36" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="D36" s="2">
+      <c r="D36" s="1">
         <v>2.0</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="s">
+      <c r="A37" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="B37" s="2" t="s">
+      <c r="B37" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="C37" s="2" t="s">
+      <c r="C37" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="D37" s="2">
+      <c r="D37" s="1">
         <v>2.0</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="s">
+      <c r="A38" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="B38" s="2" t="s">
+      <c r="B38" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="C38" s="2" t="s">
+      <c r="C38" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="D38" s="2">
+      <c r="D38" s="1">
         <v>2.0</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="s">
+      <c r="A39" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="B39" s="2" t="s">
+      <c r="B39" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="C39" s="2" t="s">
+      <c r="C39" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="D39" s="2">
+      <c r="D39" s="1">
         <v>2.0</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="s">
+      <c r="A40" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="B40" s="2" t="s">
+      <c r="B40" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="C40" s="2" t="s">
+      <c r="C40" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="D40" s="2">
+      <c r="D40" s="1">
         <v>2.0</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="s">
+      <c r="A41" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="B41" s="2" t="s">
+      <c r="B41" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="C41" s="2" t="s">
+      <c r="C41" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="D41" s="2">
+      <c r="D41" s="1">
         <v>2.0</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="s">
+      <c r="A42" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="B42" s="2" t="s">
+      <c r="B42" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="C42" s="2" t="s">
+      <c r="C42" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="D42" s="2">
+      <c r="D42" s="1">
         <v>2.0</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="s">
+      <c r="A43" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="B43" s="2" t="s">
+      <c r="B43" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="C43" s="2" t="s">
+      <c r="C43" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="D43" s="2">
+      <c r="D43" s="1">
         <v>2.0</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="s">
+      <c r="A44" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="B44" s="2" t="s">
+      <c r="B44" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="C44" s="2" t="s">
+      <c r="C44" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="D44" s="2">
+      <c r="D44" s="1">
         <v>2.0</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="s">
+      <c r="A45" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="B45" s="2" t="s">
+      <c r="B45" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="C45" s="2" t="s">
+      <c r="C45" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="D45" s="2">
+      <c r="D45" s="1">
         <v>2.0</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="s">
+      <c r="A46" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="B46" s="2" t="s">
+      <c r="B46" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="C46" s="2" t="s">
+      <c r="C46" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="D46" s="2">
+      <c r="D46" s="1">
         <v>2.0</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="s">
+      <c r="A47" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="B47" s="2" t="s">
+      <c r="B47" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="C47" s="2" t="s">
+      <c r="C47" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="D47" s="2">
+      <c r="D47" s="1">
         <v>2.0</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="s">
+      <c r="A48" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="B48" s="2" t="s">
+      <c r="B48" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="C48" s="2" t="s">
+      <c r="C48" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="D48" s="2">
+      <c r="D48" s="1">
         <v>2.0</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="s">
+      <c r="A49" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="B49" s="2" t="s">
+      <c r="B49" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="C49" s="2" t="s">
+      <c r="C49" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="D49" s="2">
+      <c r="D49" s="1">
         <v>2.0</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="s">
+      <c r="A50" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="B50" s="2" t="s">
+      <c r="B50" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="C50" s="2" t="s">
+      <c r="C50" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="D50" s="2">
+      <c r="D50" s="1">
         <v>2.0</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="s">
+      <c r="A51" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="B51" s="2" t="s">
+      <c r="B51" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="C51" s="2" t="s">
+      <c r="C51" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="D51" s="2">
+      <c r="D51" s="1">
         <v>2.0</v>
       </c>
     </row>
@@ -23263,10 +23259,10 @@
       </c>
     </row>
     <row r="62" ht="15.75" customHeight="1">
-      <c r="A62" s="2" t="s">
+      <c r="A62" s="1" t="s">
         <v>1247</v>
       </c>
-      <c r="B62" s="2" t="s">
+      <c r="B62" s="1" t="s">
         <v>1248</v>
       </c>
       <c r="C62" s="1" t="s">
@@ -25415,1402 +25411,1402 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="1" t="s">
         <v>1426</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="1" t="s">
         <v>1427</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="1" t="s">
         <v>1428</v>
       </c>
-      <c r="D2" s="2">
+      <c r="D2" s="1">
         <v>3.0</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="1" t="s">
         <v>1429</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="1" t="s">
         <v>1430</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="1" t="s">
         <v>1428</v>
       </c>
-      <c r="D3" s="2">
+      <c r="D3" s="1">
         <v>3.0</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="1" t="s">
         <v>1431</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="1" t="s">
         <v>1432</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="1" t="s">
         <v>1428</v>
       </c>
-      <c r="D4" s="2">
+      <c r="D4" s="1">
         <v>3.0</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="1" t="s">
         <v>1433</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="1" t="s">
         <v>1434</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="1" t="s">
         <v>1428</v>
       </c>
-      <c r="D5" s="2">
+      <c r="D5" s="1">
         <v>3.0</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="1" t="s">
         <v>1435</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="1" t="s">
         <v>1436</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="1" t="s">
         <v>1428</v>
       </c>
-      <c r="D6" s="2">
+      <c r="D6" s="1">
         <v>3.0</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="1" t="s">
         <v>1437</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="1" t="s">
         <v>1438</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="1" t="s">
         <v>1428</v>
       </c>
-      <c r="D7" s="2">
+      <c r="D7" s="1">
         <v>3.0</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="s">
+      <c r="A8" s="1" t="s">
         <v>1439</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="1" t="s">
         <v>1440</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" s="1" t="s">
         <v>1428</v>
       </c>
-      <c r="D8" s="2">
+      <c r="D8" s="1">
         <v>3.0</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="s">
+      <c r="A9" s="1" t="s">
         <v>1441</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="1" t="s">
         <v>1442</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" s="1" t="s">
         <v>1428</v>
       </c>
-      <c r="D9" s="2">
+      <c r="D9" s="1">
         <v>3.0</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="s">
+      <c r="A10" s="1" t="s">
         <v>1443</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="1" t="s">
         <v>1444</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C10" s="1" t="s">
         <v>1428</v>
       </c>
-      <c r="D10" s="2">
+      <c r="D10" s="1">
         <v>3.0</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="s">
+      <c r="A11" s="1" t="s">
         <v>1445</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="1" t="s">
         <v>1446</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C11" s="1" t="s">
         <v>1428</v>
       </c>
-      <c r="D11" s="2">
+      <c r="D11" s="1">
         <v>3.0</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="s">
+      <c r="A12" s="1" t="s">
         <v>1447</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="1" t="s">
         <v>1448</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="C12" s="1" t="s">
         <v>1428</v>
       </c>
-      <c r="D12" s="2">
+      <c r="D12" s="1">
         <v>3.0</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="s">
+      <c r="A13" s="1" t="s">
         <v>1449</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B13" s="1" t="s">
         <v>1450</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="C13" s="1" t="s">
         <v>1428</v>
       </c>
-      <c r="D13" s="2">
+      <c r="D13" s="1">
         <v>3.0</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="s">
+      <c r="A14" s="1" t="s">
         <v>1451</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B14" s="1" t="s">
         <v>1452</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="C14" s="1" t="s">
         <v>1428</v>
       </c>
-      <c r="D14" s="2">
+      <c r="D14" s="1">
         <v>3.0</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="s">
+      <c r="A15" s="1" t="s">
         <v>1453</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="B15" s="1" t="s">
         <v>1454</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="C15" s="1" t="s">
         <v>1428</v>
       </c>
-      <c r="D15" s="2">
+      <c r="D15" s="1">
         <v>3.0</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="s">
+      <c r="A16" s="1" t="s">
         <v>1455</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="B16" s="1" t="s">
         <v>1456</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="C16" s="1" t="s">
         <v>1428</v>
       </c>
-      <c r="D16" s="2">
+      <c r="D16" s="1">
         <v>3.0</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="s">
+      <c r="A17" s="1" t="s">
         <v>1457</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="B17" s="1" t="s">
         <v>1458</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="C17" s="1" t="s">
         <v>1428</v>
       </c>
-      <c r="D17" s="2">
+      <c r="D17" s="1">
         <v>3.0</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="s">
+      <c r="A18" s="1" t="s">
         <v>1459</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="B18" s="1" t="s">
         <v>1460</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="C18" s="1" t="s">
         <v>1428</v>
       </c>
-      <c r="D18" s="2">
+      <c r="D18" s="1">
         <v>3.0</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="s">
+      <c r="A19" s="1" t="s">
         <v>1461</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="B19" s="1" t="s">
         <v>1462</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="C19" s="1" t="s">
         <v>1428</v>
       </c>
-      <c r="D19" s="2">
+      <c r="D19" s="1">
         <v>3.0</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="s">
+      <c r="A20" s="1" t="s">
         <v>1463</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="B20" s="1" t="s">
         <v>1464</v>
       </c>
-      <c r="C20" s="2" t="s">
+      <c r="C20" s="1" t="s">
         <v>1428</v>
       </c>
-      <c r="D20" s="2">
+      <c r="D20" s="1">
         <v>3.0</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="s">
+      <c r="A21" s="1" t="s">
         <v>1465</v>
       </c>
-      <c r="B21" s="2" t="s">
+      <c r="B21" s="1" t="s">
         <v>1466</v>
       </c>
-      <c r="C21" s="2" t="s">
+      <c r="C21" s="1" t="s">
         <v>1428</v>
       </c>
-      <c r="D21" s="2">
+      <c r="D21" s="1">
         <v>3.0</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="s">
+      <c r="A22" s="1" t="s">
         <v>1467</v>
       </c>
-      <c r="B22" s="2" t="s">
+      <c r="B22" s="1" t="s">
         <v>1468</v>
       </c>
-      <c r="C22" s="2" t="s">
+      <c r="C22" s="1" t="s">
         <v>1428</v>
       </c>
-      <c r="D22" s="2">
+      <c r="D22" s="1">
         <v>3.0</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="s">
+      <c r="A23" s="1" t="s">
         <v>1469</v>
       </c>
-      <c r="B23" s="2" t="s">
+      <c r="B23" s="1" t="s">
         <v>1470</v>
       </c>
-      <c r="C23" s="2" t="s">
+      <c r="C23" s="1" t="s">
         <v>1428</v>
       </c>
-      <c r="D23" s="2">
+      <c r="D23" s="1">
         <v>3.0</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="s">
+      <c r="A24" s="1" t="s">
         <v>1471</v>
       </c>
-      <c r="B24" s="2" t="s">
+      <c r="B24" s="1" t="s">
         <v>1472</v>
       </c>
-      <c r="C24" s="2" t="s">
+      <c r="C24" s="1" t="s">
         <v>1428</v>
       </c>
-      <c r="D24" s="2">
+      <c r="D24" s="1">
         <v>3.0</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="s">
+      <c r="A25" s="1" t="s">
         <v>1473</v>
       </c>
-      <c r="B25" s="2" t="s">
+      <c r="B25" s="1" t="s">
         <v>1474</v>
       </c>
-      <c r="C25" s="2" t="s">
+      <c r="C25" s="1" t="s">
         <v>1428</v>
       </c>
-      <c r="D25" s="2">
+      <c r="D25" s="1">
         <v>3.0</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="s">
+      <c r="A26" s="1" t="s">
         <v>1475</v>
       </c>
-      <c r="B26" s="2" t="s">
+      <c r="B26" s="1" t="s">
         <v>1476</v>
       </c>
-      <c r="C26" s="2" t="s">
+      <c r="C26" s="1" t="s">
         <v>1428</v>
       </c>
-      <c r="D26" s="2">
+      <c r="D26" s="1">
         <v>3.0</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="s">
+      <c r="A27" s="1" t="s">
         <v>1477</v>
       </c>
-      <c r="B27" s="2" t="s">
+      <c r="B27" s="1" t="s">
         <v>1478</v>
       </c>
-      <c r="C27" s="2" t="s">
+      <c r="C27" s="1" t="s">
         <v>1428</v>
       </c>
-      <c r="D27" s="2">
+      <c r="D27" s="1">
         <v>3.0</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="s">
+      <c r="A28" s="1" t="s">
         <v>1479</v>
       </c>
-      <c r="B28" s="2" t="s">
+      <c r="B28" s="1" t="s">
         <v>1480</v>
       </c>
-      <c r="C28" s="2" t="s">
+      <c r="C28" s="1" t="s">
         <v>1428</v>
       </c>
-      <c r="D28" s="2">
+      <c r="D28" s="1">
         <v>3.0</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="s">
+      <c r="A29" s="1" t="s">
         <v>1481</v>
       </c>
-      <c r="B29" s="2" t="s">
+      <c r="B29" s="1" t="s">
         <v>1482</v>
       </c>
-      <c r="C29" s="2" t="s">
+      <c r="C29" s="1" t="s">
         <v>1428</v>
       </c>
-      <c r="D29" s="2">
+      <c r="D29" s="1">
         <v>3.0</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="s">
+      <c r="A30" s="1" t="s">
         <v>1483</v>
       </c>
-      <c r="B30" s="2" t="s">
+      <c r="B30" s="1" t="s">
         <v>1484</v>
       </c>
-      <c r="C30" s="2" t="s">
+      <c r="C30" s="1" t="s">
         <v>1428</v>
       </c>
-      <c r="D30" s="2">
+      <c r="D30" s="1">
         <v>3.0</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="s">
+      <c r="A31" s="1" t="s">
         <v>1485</v>
       </c>
-      <c r="B31" s="2" t="s">
+      <c r="B31" s="1" t="s">
         <v>1486</v>
       </c>
-      <c r="C31" s="2" t="s">
+      <c r="C31" s="1" t="s">
         <v>1428</v>
       </c>
-      <c r="D31" s="2">
+      <c r="D31" s="1">
         <v>3.0</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="s">
+      <c r="A32" s="1" t="s">
         <v>1487</v>
       </c>
-      <c r="B32" s="2" t="s">
+      <c r="B32" s="1" t="s">
         <v>1488</v>
       </c>
-      <c r="C32" s="2" t="s">
+      <c r="C32" s="1" t="s">
         <v>1428</v>
       </c>
-      <c r="D32" s="2">
+      <c r="D32" s="1">
         <v>3.0</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="s">
+      <c r="A33" s="1" t="s">
         <v>1489</v>
       </c>
-      <c r="B33" s="2" t="s">
+      <c r="B33" s="1" t="s">
         <v>1490</v>
       </c>
-      <c r="C33" s="2" t="s">
+      <c r="C33" s="1" t="s">
         <v>1428</v>
       </c>
-      <c r="D33" s="2">
+      <c r="D33" s="1">
         <v>3.0</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="s">
+      <c r="A34" s="1" t="s">
         <v>1491</v>
       </c>
-      <c r="B34" s="2" t="s">
+      <c r="B34" s="1" t="s">
         <v>1492</v>
       </c>
-      <c r="C34" s="2" t="s">
+      <c r="C34" s="1" t="s">
         <v>1428</v>
       </c>
-      <c r="D34" s="2">
+      <c r="D34" s="1">
         <v>3.0</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="s">
+      <c r="A35" s="1" t="s">
         <v>1493</v>
       </c>
-      <c r="B35" s="2" t="s">
+      <c r="B35" s="1" t="s">
         <v>1494</v>
       </c>
-      <c r="C35" s="2" t="s">
+      <c r="C35" s="1" t="s">
         <v>1428</v>
       </c>
-      <c r="D35" s="2">
+      <c r="D35" s="1">
         <v>3.0</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="s">
+      <c r="A36" s="1" t="s">
         <v>1495</v>
       </c>
-      <c r="B36" s="2" t="s">
+      <c r="B36" s="1" t="s">
         <v>1496</v>
       </c>
-      <c r="C36" s="2" t="s">
+      <c r="C36" s="1" t="s">
         <v>1428</v>
       </c>
-      <c r="D36" s="2">
+      <c r="D36" s="1">
         <v>3.0</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="s">
+      <c r="A37" s="1" t="s">
         <v>1497</v>
       </c>
-      <c r="B37" s="2" t="s">
+      <c r="B37" s="1" t="s">
         <v>1498</v>
       </c>
-      <c r="C37" s="2" t="s">
+      <c r="C37" s="1" t="s">
         <v>1428</v>
       </c>
-      <c r="D37" s="2">
+      <c r="D37" s="1">
         <v>3.0</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="s">
+      <c r="A38" s="1" t="s">
         <v>1499</v>
       </c>
-      <c r="B38" s="2" t="s">
+      <c r="B38" s="1" t="s">
         <v>1500</v>
       </c>
-      <c r="C38" s="2" t="s">
+      <c r="C38" s="1" t="s">
         <v>1428</v>
       </c>
-      <c r="D38" s="2">
+      <c r="D38" s="1">
         <v>3.0</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="s">
+      <c r="A39" s="1" t="s">
         <v>1501</v>
       </c>
-      <c r="B39" s="2" t="s">
+      <c r="B39" s="1" t="s">
         <v>1502</v>
       </c>
-      <c r="C39" s="2" t="s">
+      <c r="C39" s="1" t="s">
         <v>1428</v>
       </c>
-      <c r="D39" s="2">
+      <c r="D39" s="1">
         <v>3.0</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="s">
+      <c r="A40" s="1" t="s">
         <v>1503</v>
       </c>
-      <c r="B40" s="2" t="s">
+      <c r="B40" s="1" t="s">
         <v>1504</v>
       </c>
-      <c r="C40" s="2" t="s">
+      <c r="C40" s="1" t="s">
         <v>1428</v>
       </c>
-      <c r="D40" s="2">
+      <c r="D40" s="1">
         <v>3.0</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="s">
+      <c r="A41" s="1" t="s">
         <v>1505</v>
       </c>
-      <c r="B41" s="2" t="s">
+      <c r="B41" s="1" t="s">
         <v>1506</v>
       </c>
-      <c r="C41" s="2" t="s">
+      <c r="C41" s="1" t="s">
         <v>1428</v>
       </c>
-      <c r="D41" s="2">
+      <c r="D41" s="1">
         <v>3.0</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="s">
+      <c r="A42" s="1" t="s">
         <v>1507</v>
       </c>
-      <c r="B42" s="2" t="s">
+      <c r="B42" s="1" t="s">
         <v>1508</v>
       </c>
-      <c r="C42" s="2" t="s">
+      <c r="C42" s="1" t="s">
         <v>1428</v>
       </c>
-      <c r="D42" s="2">
+      <c r="D42" s="1">
         <v>3.0</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="s">
+      <c r="A43" s="1" t="s">
         <v>1509</v>
       </c>
-      <c r="B43" s="2" t="s">
+      <c r="B43" s="1" t="s">
         <v>1510</v>
       </c>
-      <c r="C43" s="2" t="s">
+      <c r="C43" s="1" t="s">
         <v>1428</v>
       </c>
-      <c r="D43" s="2">
+      <c r="D43" s="1">
         <v>3.0</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="s">
+      <c r="A44" s="1" t="s">
         <v>1511</v>
       </c>
-      <c r="B44" s="2" t="s">
+      <c r="B44" s="1" t="s">
         <v>1512</v>
       </c>
-      <c r="C44" s="2" t="s">
+      <c r="C44" s="1" t="s">
         <v>1428</v>
       </c>
-      <c r="D44" s="2">
+      <c r="D44" s="1">
         <v>3.0</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="s">
+      <c r="A45" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="B45" s="2" t="s">
+      <c r="B45" s="1" t="s">
         <v>1513</v>
       </c>
-      <c r="C45" s="2" t="s">
+      <c r="C45" s="1" t="s">
         <v>1428</v>
       </c>
-      <c r="D45" s="2">
+      <c r="D45" s="1">
         <v>3.0</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="s">
+      <c r="A46" s="1" t="s">
         <v>1514</v>
       </c>
-      <c r="B46" s="2" t="s">
+      <c r="B46" s="1" t="s">
         <v>1515</v>
       </c>
-      <c r="C46" s="2" t="s">
+      <c r="C46" s="1" t="s">
         <v>1428</v>
       </c>
-      <c r="D46" s="2">
+      <c r="D46" s="1">
         <v>3.0</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="s">
+      <c r="A47" s="1" t="s">
         <v>1516</v>
       </c>
-      <c r="B47" s="2" t="s">
+      <c r="B47" s="1" t="s">
         <v>1517</v>
       </c>
-      <c r="C47" s="2" t="s">
+      <c r="C47" s="1" t="s">
         <v>1428</v>
       </c>
-      <c r="D47" s="2">
+      <c r="D47" s="1">
         <v>3.0</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="s">
+      <c r="A48" s="1" t="s">
         <v>1518</v>
       </c>
-      <c r="B48" s="2" t="s">
+      <c r="B48" s="1" t="s">
         <v>1519</v>
       </c>
-      <c r="C48" s="2" t="s">
+      <c r="C48" s="1" t="s">
         <v>1428</v>
       </c>
-      <c r="D48" s="2">
+      <c r="D48" s="1">
         <v>3.0</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="s">
+      <c r="A49" s="1" t="s">
         <v>1520</v>
       </c>
-      <c r="B49" s="2" t="s">
+      <c r="B49" s="1" t="s">
         <v>1521</v>
       </c>
-      <c r="C49" s="2" t="s">
+      <c r="C49" s="1" t="s">
         <v>1428</v>
       </c>
-      <c r="D49" s="2">
+      <c r="D49" s="1">
         <v>3.0</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="s">
+      <c r="A50" s="1" t="s">
         <v>1522</v>
       </c>
-      <c r="B50" s="2" t="s">
+      <c r="B50" s="1" t="s">
         <v>1523</v>
       </c>
-      <c r="C50" s="2" t="s">
+      <c r="C50" s="1" t="s">
         <v>1428</v>
       </c>
-      <c r="D50" s="2">
+      <c r="D50" s="1">
         <v>3.0</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="s">
+      <c r="A51" s="1" t="s">
         <v>1524</v>
       </c>
-      <c r="B51" s="2" t="s">
+      <c r="B51" s="1" t="s">
         <v>1525</v>
       </c>
-      <c r="C51" s="2" t="s">
+      <c r="C51" s="1" t="s">
         <v>1428</v>
       </c>
-      <c r="D51" s="2">
+      <c r="D51" s="1">
         <v>3.0</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="s">
+      <c r="A52" s="1" t="s">
         <v>1526</v>
       </c>
-      <c r="B52" s="2" t="s">
+      <c r="B52" s="1" t="s">
         <v>1527</v>
       </c>
-      <c r="C52" s="2" t="s">
+      <c r="C52" s="1" t="s">
         <v>1428</v>
       </c>
-      <c r="D52" s="2">
+      <c r="D52" s="1">
         <v>3.0</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="s">
+      <c r="A53" s="1" t="s">
         <v>1528</v>
       </c>
-      <c r="B53" s="2" t="s">
+      <c r="B53" s="1" t="s">
         <v>1529</v>
       </c>
-      <c r="C53" s="2" t="s">
+      <c r="C53" s="1" t="s">
         <v>1428</v>
       </c>
-      <c r="D53" s="2">
+      <c r="D53" s="1">
         <v>3.0</v>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="s">
+      <c r="A54" s="1" t="s">
         <v>1530</v>
       </c>
-      <c r="B54" s="2" t="s">
+      <c r="B54" s="1" t="s">
         <v>1531</v>
       </c>
-      <c r="C54" s="2" t="s">
+      <c r="C54" s="1" t="s">
         <v>1428</v>
       </c>
-      <c r="D54" s="2">
+      <c r="D54" s="1">
         <v>3.0</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="s">
+      <c r="A55" s="1" t="s">
         <v>1532</v>
       </c>
-      <c r="B55" s="2" t="s">
+      <c r="B55" s="1" t="s">
         <v>1533</v>
       </c>
-      <c r="C55" s="2" t="s">
+      <c r="C55" s="1" t="s">
         <v>1428</v>
       </c>
-      <c r="D55" s="2">
+      <c r="D55" s="1">
         <v>3.0</v>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="s">
+      <c r="A56" s="1" t="s">
         <v>1534</v>
       </c>
-      <c r="B56" s="2" t="s">
+      <c r="B56" s="1" t="s">
         <v>1535</v>
       </c>
-      <c r="C56" s="2" t="s">
+      <c r="C56" s="1" t="s">
         <v>1428</v>
       </c>
-      <c r="D56" s="2">
+      <c r="D56" s="1">
         <v>3.0</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="s">
+      <c r="A57" s="1" t="s">
         <v>1536</v>
       </c>
-      <c r="B57" s="2" t="s">
+      <c r="B57" s="1" t="s">
         <v>1537</v>
       </c>
-      <c r="C57" s="2" t="s">
+      <c r="C57" s="1" t="s">
         <v>1428</v>
       </c>
-      <c r="D57" s="2">
+      <c r="D57" s="1">
         <v>3.0</v>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="s">
+      <c r="A58" s="1" t="s">
         <v>1538</v>
       </c>
-      <c r="B58" s="2" t="s">
+      <c r="B58" s="1" t="s">
         <v>1539</v>
       </c>
-      <c r="C58" s="2" t="s">
+      <c r="C58" s="1" t="s">
         <v>1428</v>
       </c>
-      <c r="D58" s="2">
+      <c r="D58" s="1">
         <v>3.0</v>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="s">
+      <c r="A59" s="1" t="s">
         <v>1540</v>
       </c>
-      <c r="B59" s="2" t="s">
+      <c r="B59" s="1" t="s">
         <v>1541</v>
       </c>
-      <c r="C59" s="2" t="s">
+      <c r="C59" s="1" t="s">
         <v>1428</v>
       </c>
-      <c r="D59" s="2">
+      <c r="D59" s="1">
         <v>3.0</v>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="s">
+      <c r="A60" s="1" t="s">
         <v>1542</v>
       </c>
-      <c r="B60" s="2" t="s">
+      <c r="B60" s="1" t="s">
         <v>1543</v>
       </c>
-      <c r="C60" s="2" t="s">
+      <c r="C60" s="1" t="s">
         <v>1428</v>
       </c>
-      <c r="D60" s="2">
+      <c r="D60" s="1">
         <v>3.0</v>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="s">
+      <c r="A61" s="1" t="s">
         <v>1544</v>
       </c>
-      <c r="B61" s="2" t="s">
+      <c r="B61" s="1" t="s">
         <v>1545</v>
       </c>
-      <c r="C61" s="2" t="s">
+      <c r="C61" s="1" t="s">
         <v>1428</v>
       </c>
-      <c r="D61" s="2">
+      <c r="D61" s="1">
         <v>3.0</v>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="s">
+      <c r="A62" s="1" t="s">
         <v>1546</v>
       </c>
-      <c r="B62" s="2" t="s">
+      <c r="B62" s="1" t="s">
         <v>1547</v>
       </c>
-      <c r="C62" s="2" t="s">
+      <c r="C62" s="1" t="s">
         <v>1428</v>
       </c>
-      <c r="D62" s="2">
+      <c r="D62" s="1">
         <v>3.0</v>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="2" t="s">
+      <c r="A63" s="1" t="s">
         <v>1548</v>
       </c>
-      <c r="B63" s="2" t="s">
+      <c r="B63" s="1" t="s">
         <v>1549</v>
       </c>
-      <c r="C63" s="2" t="s">
+      <c r="C63" s="1" t="s">
         <v>1428</v>
       </c>
-      <c r="D63" s="2">
+      <c r="D63" s="1">
         <v>3.0</v>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="s">
+      <c r="A64" s="1" t="s">
         <v>1550</v>
       </c>
-      <c r="B64" s="2" t="s">
+      <c r="B64" s="1" t="s">
         <v>1551</v>
       </c>
-      <c r="C64" s="2" t="s">
+      <c r="C64" s="1" t="s">
         <v>1428</v>
       </c>
-      <c r="D64" s="2">
+      <c r="D64" s="1">
         <v>3.0</v>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="s">
+      <c r="A65" s="1" t="s">
         <v>1552</v>
       </c>
-      <c r="B65" s="2" t="s">
+      <c r="B65" s="1" t="s">
         <v>1553</v>
       </c>
-      <c r="C65" s="2" t="s">
+      <c r="C65" s="1" t="s">
         <v>1428</v>
       </c>
-      <c r="D65" s="2">
+      <c r="D65" s="1">
         <v>3.0</v>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="2" t="s">
+      <c r="A66" s="1" t="s">
         <v>1554</v>
       </c>
-      <c r="B66" s="2" t="s">
+      <c r="B66" s="1" t="s">
         <v>1555</v>
       </c>
-      <c r="C66" s="2" t="s">
+      <c r="C66" s="1" t="s">
         <v>1428</v>
       </c>
-      <c r="D66" s="2">
+      <c r="D66" s="1">
         <v>3.0</v>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="s">
+      <c r="A67" s="1" t="s">
         <v>1556</v>
       </c>
-      <c r="B67" s="2" t="s">
+      <c r="B67" s="1" t="s">
         <v>1557</v>
       </c>
-      <c r="C67" s="2" t="s">
+      <c r="C67" s="1" t="s">
         <v>1428</v>
       </c>
-      <c r="D67" s="2">
+      <c r="D67" s="1">
         <v>3.0</v>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="s">
+      <c r="A68" s="1" t="s">
         <v>1558</v>
       </c>
-      <c r="B68" s="2" t="s">
+      <c r="B68" s="1" t="s">
         <v>1559</v>
       </c>
-      <c r="C68" s="2" t="s">
+      <c r="C68" s="1" t="s">
         <v>1428</v>
       </c>
-      <c r="D68" s="2">
+      <c r="D68" s="1">
         <v>3.0</v>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="2" t="s">
+      <c r="A69" s="1" t="s">
         <v>1560</v>
       </c>
-      <c r="B69" s="2" t="s">
+      <c r="B69" s="1" t="s">
         <v>1561</v>
       </c>
-      <c r="C69" s="2" t="s">
+      <c r="C69" s="1" t="s">
         <v>1428</v>
       </c>
-      <c r="D69" s="2">
+      <c r="D69" s="1">
         <v>3.0</v>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="2" t="s">
+      <c r="A70" s="1" t="s">
         <v>1562</v>
       </c>
-      <c r="B70" s="2" t="s">
+      <c r="B70" s="1" t="s">
         <v>1563</v>
       </c>
-      <c r="C70" s="2" t="s">
+      <c r="C70" s="1" t="s">
         <v>1428</v>
       </c>
-      <c r="D70" s="2">
+      <c r="D70" s="1">
         <v>3.0</v>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="2" t="s">
+      <c r="A71" s="1" t="s">
         <v>1564</v>
       </c>
-      <c r="B71" s="2" t="s">
+      <c r="B71" s="1" t="s">
         <v>1565</v>
       </c>
-      <c r="C71" s="2" t="s">
+      <c r="C71" s="1" t="s">
         <v>1428</v>
       </c>
-      <c r="D71" s="2">
+      <c r="D71" s="1">
         <v>3.0</v>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="2" t="s">
+      <c r="A72" s="1" t="s">
         <v>1566</v>
       </c>
-      <c r="B72" s="2" t="s">
+      <c r="B72" s="1" t="s">
         <v>1567</v>
       </c>
-      <c r="C72" s="2" t="s">
+      <c r="C72" s="1" t="s">
         <v>1428</v>
       </c>
-      <c r="D72" s="2">
+      <c r="D72" s="1">
         <v>3.0</v>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="2" t="s">
+      <c r="A73" s="1" t="s">
         <v>1568</v>
       </c>
-      <c r="B73" s="2" t="s">
+      <c r="B73" s="1" t="s">
         <v>1569</v>
       </c>
-      <c r="C73" s="2" t="s">
+      <c r="C73" s="1" t="s">
         <v>1428</v>
       </c>
-      <c r="D73" s="2">
+      <c r="D73" s="1">
         <v>3.0</v>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="2" t="s">
+      <c r="A74" s="1" t="s">
         <v>1570</v>
       </c>
-      <c r="B74" s="2" t="s">
+      <c r="B74" s="1" t="s">
         <v>1571</v>
       </c>
-      <c r="C74" s="2" t="s">
+      <c r="C74" s="1" t="s">
         <v>1428</v>
       </c>
-      <c r="D74" s="2">
+      <c r="D74" s="1">
         <v>3.0</v>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="2" t="s">
+      <c r="A75" s="1" t="s">
         <v>1572</v>
       </c>
-      <c r="B75" s="2" t="s">
+      <c r="B75" s="1" t="s">
         <v>1573</v>
       </c>
-      <c r="C75" s="2" t="s">
+      <c r="C75" s="1" t="s">
         <v>1428</v>
       </c>
-      <c r="D75" s="2">
+      <c r="D75" s="1">
         <v>3.0</v>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="2" t="s">
+      <c r="A76" s="1" t="s">
         <v>1574</v>
       </c>
-      <c r="B76" s="2" t="s">
+      <c r="B76" s="1" t="s">
         <v>1575</v>
       </c>
-      <c r="C76" s="2" t="s">
+      <c r="C76" s="1" t="s">
         <v>1428</v>
       </c>
-      <c r="D76" s="2">
+      <c r="D76" s="1">
         <v>3.0</v>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="2" t="s">
+      <c r="A77" s="1" t="s">
         <v>1576</v>
       </c>
-      <c r="B77" s="2" t="s">
+      <c r="B77" s="1" t="s">
         <v>1577</v>
       </c>
-      <c r="C77" s="2" t="s">
+      <c r="C77" s="1" t="s">
         <v>1428</v>
       </c>
-      <c r="D77" s="2">
+      <c r="D77" s="1">
         <v>3.0</v>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="2" t="s">
+      <c r="A78" s="1" t="s">
         <v>1578</v>
       </c>
-      <c r="B78" s="2" t="s">
+      <c r="B78" s="1" t="s">
         <v>1579</v>
       </c>
-      <c r="C78" s="2" t="s">
+      <c r="C78" s="1" t="s">
         <v>1428</v>
       </c>
-      <c r="D78" s="2">
+      <c r="D78" s="1">
         <v>3.0</v>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="2" t="s">
+      <c r="A79" s="1" t="s">
         <v>1580</v>
       </c>
-      <c r="B79" s="2" t="s">
+      <c r="B79" s="1" t="s">
         <v>1581</v>
       </c>
-      <c r="C79" s="2" t="s">
+      <c r="C79" s="1" t="s">
         <v>1428</v>
       </c>
-      <c r="D79" s="2">
+      <c r="D79" s="1">
         <v>3.0</v>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="2" t="s">
+      <c r="A80" s="1" t="s">
         <v>1582</v>
       </c>
-      <c r="B80" s="2" t="s">
+      <c r="B80" s="1" t="s">
         <v>1583</v>
       </c>
-      <c r="C80" s="2" t="s">
+      <c r="C80" s="1" t="s">
         <v>1428</v>
       </c>
-      <c r="D80" s="2">
+      <c r="D80" s="1">
         <v>3.0</v>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="2" t="s">
+      <c r="A81" s="1" t="s">
         <v>1584</v>
       </c>
-      <c r="B81" s="2" t="s">
+      <c r="B81" s="1" t="s">
         <v>1585</v>
       </c>
-      <c r="C81" s="2" t="s">
+      <c r="C81" s="1" t="s">
         <v>1428</v>
       </c>
-      <c r="D81" s="2">
+      <c r="D81" s="1">
         <v>3.0</v>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="2" t="s">
+      <c r="A82" s="1" t="s">
         <v>1586</v>
       </c>
-      <c r="B82" s="2" t="s">
+      <c r="B82" s="1" t="s">
         <v>1587</v>
       </c>
-      <c r="C82" s="2" t="s">
+      <c r="C82" s="1" t="s">
         <v>1428</v>
       </c>
-      <c r="D82" s="2">
+      <c r="D82" s="1">
         <v>3.0</v>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="2" t="s">
+      <c r="A83" s="1" t="s">
         <v>1588</v>
       </c>
-      <c r="B83" s="2" t="s">
+      <c r="B83" s="1" t="s">
         <v>1589</v>
       </c>
-      <c r="C83" s="2" t="s">
+      <c r="C83" s="1" t="s">
         <v>1428</v>
       </c>
-      <c r="D83" s="2">
+      <c r="D83" s="1">
         <v>3.0</v>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="2" t="s">
+      <c r="A84" s="1" t="s">
         <v>1590</v>
       </c>
-      <c r="B84" s="2" t="s">
+      <c r="B84" s="1" t="s">
         <v>1591</v>
       </c>
-      <c r="C84" s="2" t="s">
+      <c r="C84" s="1" t="s">
         <v>1428</v>
       </c>
-      <c r="D84" s="2">
+      <c r="D84" s="1">
         <v>3.0</v>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="2" t="s">
+      <c r="A85" s="1" t="s">
         <v>1592</v>
       </c>
-      <c r="B85" s="2" t="s">
+      <c r="B85" s="1" t="s">
         <v>1593</v>
       </c>
-      <c r="C85" s="2" t="s">
+      <c r="C85" s="1" t="s">
         <v>1428</v>
       </c>
-      <c r="D85" s="2">
+      <c r="D85" s="1">
         <v>3.0</v>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="2" t="s">
+      <c r="A86" s="1" t="s">
         <v>1594</v>
       </c>
-      <c r="B86" s="2" t="s">
+      <c r="B86" s="1" t="s">
         <v>1595</v>
       </c>
-      <c r="C86" s="2" t="s">
+      <c r="C86" s="1" t="s">
         <v>1428</v>
       </c>
-      <c r="D86" s="2">
+      <c r="D86" s="1">
         <v>3.0</v>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="2" t="s">
+      <c r="A87" s="1" t="s">
         <v>1596</v>
       </c>
-      <c r="B87" s="2" t="s">
+      <c r="B87" s="1" t="s">
         <v>1597</v>
       </c>
-      <c r="C87" s="2" t="s">
+      <c r="C87" s="1" t="s">
         <v>1428</v>
       </c>
-      <c r="D87" s="2">
+      <c r="D87" s="1">
         <v>3.0</v>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="2" t="s">
+      <c r="A88" s="1" t="s">
         <v>1598</v>
       </c>
-      <c r="B88" s="2" t="s">
+      <c r="B88" s="1" t="s">
         <v>1599</v>
       </c>
-      <c r="C88" s="2" t="s">
+      <c r="C88" s="1" t="s">
         <v>1428</v>
       </c>
-      <c r="D88" s="2">
+      <c r="D88" s="1">
         <v>3.0</v>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="2" t="s">
+      <c r="A89" s="1" t="s">
         <v>1600</v>
       </c>
-      <c r="B89" s="2" t="s">
+      <c r="B89" s="1" t="s">
         <v>1601</v>
       </c>
-      <c r="C89" s="2" t="s">
+      <c r="C89" s="1" t="s">
         <v>1428</v>
       </c>
-      <c r="D89" s="2">
+      <c r="D89" s="1">
         <v>3.0</v>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="2" t="s">
+      <c r="A90" s="1" t="s">
         <v>1602</v>
       </c>
-      <c r="B90" s="2" t="s">
+      <c r="B90" s="1" t="s">
         <v>1603</v>
       </c>
-      <c r="C90" s="2" t="s">
+      <c r="C90" s="1" t="s">
         <v>1428</v>
       </c>
-      <c r="D90" s="2">
+      <c r="D90" s="1">
         <v>3.0</v>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="2" t="s">
+      <c r="A91" s="1" t="s">
         <v>1604</v>
       </c>
-      <c r="B91" s="2" t="s">
+      <c r="B91" s="1" t="s">
         <v>1605</v>
       </c>
-      <c r="C91" s="2" t="s">
+      <c r="C91" s="1" t="s">
         <v>1428</v>
       </c>
-      <c r="D91" s="2">
+      <c r="D91" s="1">
         <v>3.0</v>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="2" t="s">
+      <c r="A92" s="1" t="s">
         <v>1606</v>
       </c>
-      <c r="B92" s="2" t="s">
+      <c r="B92" s="1" t="s">
         <v>1607</v>
       </c>
-      <c r="C92" s="2" t="s">
+      <c r="C92" s="1" t="s">
         <v>1428</v>
       </c>
-      <c r="D92" s="2">
+      <c r="D92" s="1">
         <v>3.0</v>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="2" t="s">
+      <c r="A93" s="1" t="s">
         <v>1608</v>
       </c>
-      <c r="B93" s="2" t="s">
+      <c r="B93" s="1" t="s">
         <v>1609</v>
       </c>
-      <c r="C93" s="2" t="s">
+      <c r="C93" s="1" t="s">
         <v>1428</v>
       </c>
-      <c r="D93" s="2">
+      <c r="D93" s="1">
         <v>3.0</v>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="2" t="s">
+      <c r="A94" s="1" t="s">
         <v>1610</v>
       </c>
-      <c r="B94" s="2" t="s">
+      <c r="B94" s="1" t="s">
         <v>1611</v>
       </c>
-      <c r="C94" s="2" t="s">
+      <c r="C94" s="1" t="s">
         <v>1428</v>
       </c>
-      <c r="D94" s="2">
+      <c r="D94" s="1">
         <v>3.0</v>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="2" t="s">
+      <c r="A95" s="1" t="s">
         <v>1612</v>
       </c>
-      <c r="B95" s="2" t="s">
+      <c r="B95" s="1" t="s">
         <v>1613</v>
       </c>
-      <c r="C95" s="2" t="s">
+      <c r="C95" s="1" t="s">
         <v>1428</v>
       </c>
-      <c r="D95" s="2">
+      <c r="D95" s="1">
         <v>3.0</v>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="2" t="s">
+      <c r="A96" s="1" t="s">
         <v>1614</v>
       </c>
-      <c r="B96" s="2" t="s">
+      <c r="B96" s="1" t="s">
         <v>1615</v>
       </c>
-      <c r="C96" s="2" t="s">
+      <c r="C96" s="1" t="s">
         <v>1428</v>
       </c>
-      <c r="D96" s="2">
+      <c r="D96" s="1">
         <v>3.0</v>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="2" t="s">
+      <c r="A97" s="1" t="s">
         <v>1616</v>
       </c>
-      <c r="B97" s="2" t="s">
+      <c r="B97" s="1" t="s">
         <v>1617</v>
       </c>
-      <c r="C97" s="2" t="s">
+      <c r="C97" s="1" t="s">
         <v>1428</v>
       </c>
-      <c r="D97" s="2">
+      <c r="D97" s="1">
         <v>3.0</v>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="2" t="s">
+      <c r="A98" s="1" t="s">
         <v>1618</v>
       </c>
-      <c r="B98" s="2" t="s">
+      <c r="B98" s="1" t="s">
         <v>1619</v>
       </c>
-      <c r="C98" s="2" t="s">
+      <c r="C98" s="1" t="s">
         <v>1428</v>
       </c>
-      <c r="D98" s="2">
+      <c r="D98" s="1">
         <v>3.0</v>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="2">
+      <c r="A99" s="1">
         <v>0.0</v>
       </c>
-      <c r="B99" s="2" t="s">
+      <c r="B99" s="1" t="s">
         <v>1620</v>
       </c>
-      <c r="C99" s="2" t="s">
+      <c r="C99" s="1" t="s">
         <v>1428</v>
       </c>
-      <c r="D99" s="2">
+      <c r="D99" s="1">
         <v>3.0</v>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="2" t="s">
+      <c r="A100" s="1" t="s">
         <v>1621</v>
       </c>
-      <c r="B100" s="2" t="s">
+      <c r="B100" s="1" t="s">
         <v>1622</v>
       </c>
-      <c r="C100" s="2" t="s">
+      <c r="C100" s="1" t="s">
         <v>1428</v>
       </c>
-      <c r="D100" s="2">
+      <c r="D100" s="1">
         <v>3.0</v>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="2" t="s">
+      <c r="A101" s="1" t="s">
         <v>1623</v>
       </c>
-      <c r="B101" s="2" t="s">
+      <c r="B101" s="1" t="s">
         <v>1624</v>
       </c>
-      <c r="C101" s="2" t="s">
+      <c r="C101" s="1" t="s">
         <v>1428</v>
       </c>
-      <c r="D101" s="2">
+      <c r="D101" s="1">
         <v>3.0</v>
       </c>
     </row>
